--- a/docs/oc-mensuales/articulos-de-aseo-e-higiene/abr-2026.xlsx
+++ b/docs/oc-mensuales/articulos-de-aseo-e-higiene/abr-2026.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OC abr-2026" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="OC abr-2026" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -854,7 +854,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -976,7 +976,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1708,7 +1708,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2135,7 +2135,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -2318,7 +2318,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -2440,7 +2440,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -2501,7 +2501,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -2562,7 +2562,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -2623,7 +2623,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -3050,7 +3050,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -3599,7 +3599,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -3843,7 +3843,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -4514,7 +4514,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -4880,7 +4880,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -5002,7 +5002,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -5246,7 +5246,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -5551,7 +5551,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -5734,7 +5734,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -6283,7 +6283,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -6344,7 +6344,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
@@ -6954,7 +6954,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
@@ -7076,7 +7076,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
@@ -7259,7 +7259,7 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
@@ -7823,7 +7823,7 @@
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="L121" t="inlineStr">
@@ -9093,7 +9093,7 @@
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
@@ -9154,7 +9154,7 @@
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
@@ -9398,7 +9398,7 @@
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
@@ -9703,7 +9703,7 @@
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
@@ -10130,7 +10130,7 @@
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
@@ -10252,7 +10252,7 @@
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
@@ -10435,7 +10435,7 @@
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
@@ -10801,7 +10801,7 @@
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
@@ -10862,7 +10862,7 @@
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
@@ -10923,7 +10923,7 @@
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
@@ -11045,7 +11045,7 @@
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
@@ -11167,7 +11167,7 @@
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
@@ -12082,7 +12082,7 @@
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I191" t="inlineStr">
@@ -12265,7 +12265,7 @@
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
@@ -12448,7 +12448,7 @@
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I197" t="inlineStr">
@@ -12753,7 +12753,7 @@
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I202" t="inlineStr">
@@ -13180,7 +13180,7 @@
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I209" t="inlineStr">
@@ -13363,7 +13363,7 @@
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I212" t="inlineStr">
@@ -13973,7 +13973,7 @@
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I222" t="inlineStr">
@@ -14583,7 +14583,7 @@
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I232" t="inlineStr">
@@ -15193,7 +15193,7 @@
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I242" t="inlineStr">
@@ -15803,7 +15803,7 @@
       </c>
       <c r="H252" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I252" t="inlineStr">
@@ -16108,7 +16108,7 @@
       </c>
       <c r="H257" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I257" t="inlineStr">
@@ -16718,7 +16718,7 @@
       </c>
       <c r="H267" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I267" t="inlineStr">
@@ -16840,7 +16840,7 @@
       </c>
       <c r="H269" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I269" t="inlineStr">
@@ -16962,7 +16962,7 @@
       </c>
       <c r="H271" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I271" t="inlineStr">
@@ -17206,7 +17206,7 @@
       </c>
       <c r="H275" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I275" t="inlineStr">
@@ -17328,7 +17328,7 @@
       </c>
       <c r="H277" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I277" t="inlineStr">
@@ -17389,7 +17389,7 @@
       </c>
       <c r="H278" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I278" t="inlineStr">
@@ -17511,7 +17511,7 @@
       </c>
       <c r="H280" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I280" t="inlineStr">
@@ -17694,7 +17694,7 @@
       </c>
       <c r="H283" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I283" t="inlineStr">
@@ -17816,7 +17816,7 @@
       </c>
       <c r="H285" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I285" t="inlineStr">
@@ -17877,7 +17877,7 @@
       </c>
       <c r="H286" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I286" t="inlineStr">
@@ -18426,7 +18426,7 @@
       </c>
       <c r="H295" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I295" t="inlineStr">
@@ -18609,7 +18609,7 @@
       </c>
       <c r="H298" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I298" t="inlineStr">
@@ -18853,7 +18853,7 @@
       </c>
       <c r="H302" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I302" t="inlineStr">
@@ -18914,7 +18914,7 @@
       </c>
       <c r="H303" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I303" t="inlineStr">
@@ -19219,7 +19219,7 @@
       </c>
       <c r="H308" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I308" t="inlineStr">
@@ -20378,7 +20378,7 @@
       </c>
       <c r="H327" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I327" t="inlineStr">
@@ -20500,7 +20500,7 @@
       </c>
       <c r="H329" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I329" t="inlineStr">
@@ -20988,7 +20988,7 @@
       </c>
       <c r="H337" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I337" t="inlineStr">
@@ -21049,7 +21049,7 @@
       </c>
       <c r="H338" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I338" t="inlineStr">
@@ -21903,7 +21903,7 @@
       </c>
       <c r="H352" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I352" t="inlineStr">
@@ -22208,7 +22208,7 @@
       </c>
       <c r="H357" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I357" t="inlineStr">
@@ -22650,7 +22650,7 @@
       </c>
       <c r="K364" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="L364" t="inlineStr">
@@ -22776,7 +22776,7 @@
       </c>
       <c r="K366" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="L366" t="inlineStr">
@@ -23070,7 +23070,7 @@
       </c>
       <c r="H371" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I371" t="inlineStr">
@@ -23146,7 +23146,7 @@
       </c>
       <c r="K372" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="L372" t="inlineStr">
@@ -23196,7 +23196,7 @@
       </c>
       <c r="H373" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I373" t="inlineStr">
@@ -23318,7 +23318,7 @@
       </c>
       <c r="H375" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I375" t="inlineStr">
@@ -24172,7 +24172,7 @@
       </c>
       <c r="H389" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I389" t="inlineStr">
@@ -24233,7 +24233,7 @@
       </c>
       <c r="H390" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I390" t="inlineStr">
@@ -24477,7 +24477,7 @@
       </c>
       <c r="H394" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I394" t="inlineStr">
@@ -24965,7 +24965,7 @@
       </c>
       <c r="H402" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I402" t="inlineStr">
@@ -25026,7 +25026,7 @@
       </c>
       <c r="H403" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I403" t="inlineStr">
@@ -25819,7 +25819,7 @@
       </c>
       <c r="H416" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I416" t="inlineStr">
@@ -25880,7 +25880,7 @@
       </c>
       <c r="H417" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I417" t="inlineStr">
@@ -26063,7 +26063,7 @@
       </c>
       <c r="H420" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I420" t="inlineStr">
@@ -26612,7 +26612,7 @@
       </c>
       <c r="H429" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I429" t="inlineStr">
@@ -27344,7 +27344,7 @@
       </c>
       <c r="H441" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I441" t="inlineStr">
@@ -27649,7 +27649,7 @@
       </c>
       <c r="H446" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I446" t="inlineStr">
@@ -28198,7 +28198,7 @@
       </c>
       <c r="H455" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I455" t="inlineStr">
@@ -28625,7 +28625,7 @@
       </c>
       <c r="H462" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I462" t="inlineStr">
@@ -28747,7 +28747,7 @@
       </c>
       <c r="H464" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I464" t="inlineStr">
@@ -28808,7 +28808,7 @@
       </c>
       <c r="H465" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I465" t="inlineStr">
@@ -28930,7 +28930,7 @@
       </c>
       <c r="H467" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I467" t="inlineStr">
@@ -29052,7 +29052,7 @@
       </c>
       <c r="H469" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I469" t="inlineStr">
@@ -30089,7 +30089,7 @@
       </c>
       <c r="H486" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I486" t="inlineStr">
@@ -30394,7 +30394,7 @@
       </c>
       <c r="H491" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I491" t="inlineStr">
@@ -31248,7 +31248,7 @@
       </c>
       <c r="H505" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I505" t="inlineStr">
@@ -31370,7 +31370,7 @@
       </c>
       <c r="H507" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I507" t="inlineStr">
@@ -31614,7 +31614,7 @@
       </c>
       <c r="H511" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I511" t="inlineStr">
@@ -32163,7 +32163,7 @@
       </c>
       <c r="H520" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I520" t="inlineStr">
@@ -32285,7 +32285,7 @@
       </c>
       <c r="H522" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I522" t="inlineStr">
@@ -32346,7 +32346,7 @@
       </c>
       <c r="H523" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I523" t="inlineStr">
@@ -33078,7 +33078,7 @@
       </c>
       <c r="H535" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I535" t="inlineStr">
@@ -33200,7 +33200,7 @@
       </c>
       <c r="H537" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I537" t="inlineStr">
@@ -33261,7 +33261,7 @@
       </c>
       <c r="H538" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I538" t="inlineStr">
@@ -33505,7 +33505,7 @@
       </c>
       <c r="H542" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I542" t="inlineStr">
@@ -33627,7 +33627,7 @@
       </c>
       <c r="H544" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I544" t="inlineStr">
@@ -33688,7 +33688,7 @@
       </c>
       <c r="H545" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I545" t="inlineStr">
@@ -33810,7 +33810,7 @@
       </c>
       <c r="H547" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I547" t="inlineStr">
@@ -33871,7 +33871,7 @@
       </c>
       <c r="H548" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I548" t="inlineStr">
@@ -34664,7 +34664,7 @@
       </c>
       <c r="H561" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I561" t="inlineStr">
@@ -34847,7 +34847,7 @@
       </c>
       <c r="H564" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I564" t="inlineStr">
@@ -34908,7 +34908,7 @@
       </c>
       <c r="H565" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I565" t="inlineStr">
@@ -36006,7 +36006,7 @@
       </c>
       <c r="H583" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I583" t="inlineStr">
@@ -36433,7 +36433,7 @@
       </c>
       <c r="H590" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I590" t="inlineStr">
@@ -37470,7 +37470,7 @@
       </c>
       <c r="H607" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I607" t="inlineStr">
@@ -37592,7 +37592,7 @@
       </c>
       <c r="H609" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I609" t="inlineStr">
@@ -37897,7 +37897,7 @@
       </c>
       <c r="H614" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I614" t="inlineStr">
@@ -38080,7 +38080,7 @@
       </c>
       <c r="H617" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I617" t="inlineStr">
@@ -38263,7 +38263,7 @@
       </c>
       <c r="H620" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I620" t="inlineStr">
@@ -38385,7 +38385,7 @@
       </c>
       <c r="H622" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I622" t="inlineStr">
@@ -38446,7 +38446,7 @@
       </c>
       <c r="H623" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I623" t="inlineStr">
@@ -38568,7 +38568,7 @@
       </c>
       <c r="H625" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I625" t="inlineStr">
@@ -38934,7 +38934,7 @@
       </c>
       <c r="H631" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I631" t="inlineStr">
@@ -39498,7 +39498,7 @@
       </c>
       <c r="K640" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="L640" t="inlineStr">
@@ -39853,7 +39853,7 @@
       </c>
       <c r="H646" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I646" t="inlineStr">
@@ -40707,7 +40707,7 @@
       </c>
       <c r="H660" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I660" t="inlineStr">
@@ -40829,7 +40829,7 @@
       </c>
       <c r="H662" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I662" t="inlineStr">
@@ -41988,7 +41988,7 @@
       </c>
       <c r="H681" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I681" t="inlineStr">
@@ -42232,7 +42232,7 @@
       </c>
       <c r="H685" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I685" t="inlineStr">
@@ -43086,7 +43086,7 @@
       </c>
       <c r="H699" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I699" t="inlineStr">
@@ -43147,7 +43147,7 @@
       </c>
       <c r="H700" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I700" t="inlineStr">
@@ -44062,7 +44062,7 @@
       </c>
       <c r="H715" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I715" t="inlineStr">
@@ -44184,7 +44184,7 @@
       </c>
       <c r="H717" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I717" t="inlineStr">
@@ -44489,7 +44489,7 @@
       </c>
       <c r="H722" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I722" t="inlineStr">
@@ -44611,7 +44611,7 @@
       </c>
       <c r="H724" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I724" t="inlineStr">
@@ -44855,7 +44855,7 @@
       </c>
       <c r="H728" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I728" t="inlineStr">
@@ -45282,7 +45282,7 @@
       </c>
       <c r="H735" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I735" t="inlineStr">
@@ -45526,7 +45526,7 @@
       </c>
       <c r="H739" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I739" t="inlineStr">
@@ -46990,7 +46990,7 @@
       </c>
       <c r="H763" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I763" t="inlineStr">
@@ -47966,7 +47966,7 @@
       </c>
       <c r="H779" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I779" t="inlineStr">
@@ -48332,7 +48332,7 @@
       </c>
       <c r="H785" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I785" t="inlineStr">
@@ -49064,7 +49064,7 @@
       </c>
       <c r="H797" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I797" t="inlineStr">
@@ -49125,7 +49125,7 @@
       </c>
       <c r="H798" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I798" t="inlineStr">
@@ -49186,7 +49186,7 @@
       </c>
       <c r="H799" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I799" t="inlineStr">
@@ -49247,7 +49247,7 @@
       </c>
       <c r="H800" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I800" t="inlineStr">
@@ -49369,7 +49369,7 @@
       </c>
       <c r="H802" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I802" t="inlineStr">
@@ -49552,7 +49552,7 @@
       </c>
       <c r="H805" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I805" t="inlineStr">
@@ -49613,7 +49613,7 @@
       </c>
       <c r="H806" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I806" t="inlineStr">
@@ -49674,7 +49674,7 @@
       </c>
       <c r="H807" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I807" t="inlineStr">
@@ -50162,7 +50162,7 @@
       </c>
       <c r="H815" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I815" t="inlineStr">
@@ -50467,7 +50467,7 @@
       </c>
       <c r="H820" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I820" t="inlineStr">
@@ -50894,7 +50894,7 @@
       </c>
       <c r="H827" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I827" t="inlineStr">
@@ -51260,7 +51260,7 @@
       </c>
       <c r="H833" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I833" t="inlineStr">
@@ -51321,7 +51321,7 @@
       </c>
       <c r="H834" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I834" t="inlineStr">
@@ -51565,7 +51565,7 @@
       </c>
       <c r="H838" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I838" t="inlineStr">
@@ -51931,7 +51931,7 @@
       </c>
       <c r="H844" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I844" t="inlineStr">
@@ -53151,7 +53151,7 @@
       </c>
       <c r="H864" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I864" t="inlineStr">
@@ -53273,7 +53273,7 @@
       </c>
       <c r="H866" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I866" t="inlineStr">
@@ -53639,7 +53639,7 @@
       </c>
       <c r="H872" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I872" t="inlineStr">
@@ -53700,7 +53700,7 @@
       </c>
       <c r="H873" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I873" t="inlineStr">
@@ -53883,7 +53883,7 @@
       </c>
       <c r="H876" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I876" t="inlineStr">
@@ -54310,7 +54310,7 @@
       </c>
       <c r="H883" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I883" t="inlineStr">
@@ -54432,7 +54432,7 @@
       </c>
       <c r="H885" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I885" t="inlineStr">
@@ -54798,7 +54798,7 @@
       </c>
       <c r="H891" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I891" t="inlineStr">
@@ -54859,7 +54859,7 @@
       </c>
       <c r="H892" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I892" t="inlineStr">
@@ -54920,7 +54920,7 @@
       </c>
       <c r="H893" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I893" t="inlineStr">
@@ -55530,7 +55530,7 @@
       </c>
       <c r="H903" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I903" t="inlineStr">
@@ -55774,7 +55774,7 @@
       </c>
       <c r="H907" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I907" t="inlineStr">
@@ -55835,7 +55835,7 @@
       </c>
       <c r="H908" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I908" t="inlineStr">
@@ -55896,7 +55896,7 @@
       </c>
       <c r="H909" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I909" t="inlineStr">
@@ -56323,7 +56323,7 @@
       </c>
       <c r="H916" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I916" t="inlineStr">
@@ -56689,7 +56689,7 @@
       </c>
       <c r="H922" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I922" t="inlineStr">
@@ -56811,7 +56811,7 @@
       </c>
       <c r="H924" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I924" t="inlineStr">
@@ -57360,7 +57360,7 @@
       </c>
       <c r="H933" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I933" t="inlineStr">
@@ -57787,7 +57787,7 @@
       </c>
       <c r="H940" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I940" t="inlineStr">
@@ -58153,7 +58153,7 @@
       </c>
       <c r="H946" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I946" t="inlineStr">
@@ -58763,7 +58763,7 @@
       </c>
       <c r="H956" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I956" t="inlineStr">
@@ -59068,7 +59068,7 @@
       </c>
       <c r="H961" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I961" t="inlineStr">
@@ -59251,7 +59251,7 @@
       </c>
       <c r="H964" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I964" t="inlineStr">
@@ -59434,7 +59434,7 @@
       </c>
       <c r="H967" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I967" t="inlineStr">
@@ -59617,7 +59617,7 @@
       </c>
       <c r="H970" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I970" t="inlineStr">
@@ -59739,7 +59739,7 @@
       </c>
       <c r="H972" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I972" t="inlineStr">
@@ -59922,7 +59922,7 @@
       </c>
       <c r="H975" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I975" t="inlineStr">
@@ -59983,7 +59983,7 @@
       </c>
       <c r="H976" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I976" t="inlineStr">
@@ -60349,7 +60349,7 @@
       </c>
       <c r="H982" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I982" t="inlineStr">
@@ -61569,7 +61569,7 @@
       </c>
       <c r="H1002" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I1002" t="inlineStr">
@@ -61630,7 +61630,7 @@
       </c>
       <c r="H1003" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I1003" t="inlineStr">
@@ -61813,7 +61813,7 @@
       </c>
       <c r="H1006" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I1006" t="inlineStr">
@@ -62362,7 +62362,7 @@
       </c>
       <c r="H1015" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I1015" t="inlineStr">
@@ -62484,7 +62484,7 @@
       </c>
       <c r="H1017" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I1017" t="inlineStr">
@@ -62606,7 +62606,7 @@
       </c>
       <c r="H1019" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I1019" t="inlineStr">
@@ -62850,7 +62850,7 @@
       </c>
       <c r="H1023" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I1023" t="inlineStr">
@@ -63094,7 +63094,7 @@
       </c>
       <c r="H1027" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I1027" t="inlineStr">
@@ -63460,7 +63460,7 @@
       </c>
       <c r="H1033" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I1033" t="inlineStr">
@@ -63826,7 +63826,7 @@
       </c>
       <c r="H1039" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I1039" t="inlineStr">
@@ -64131,7 +64131,7 @@
       </c>
       <c r="H1044" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I1044" t="inlineStr">
@@ -64192,7 +64192,7 @@
       </c>
       <c r="H1045" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I1045" t="inlineStr">
@@ -64741,7 +64741,7 @@
       </c>
       <c r="H1054" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I1054" t="inlineStr">
@@ -64863,7 +64863,7 @@
       </c>
       <c r="H1056" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I1056" t="inlineStr">
@@ -64924,7 +64924,7 @@
       </c>
       <c r="H1057" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I1057" t="inlineStr">
@@ -65412,7 +65412,7 @@
       </c>
       <c r="H1065" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I1065" t="inlineStr">
@@ -66266,7 +66266,7 @@
       </c>
       <c r="H1079" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I1079" t="inlineStr">
@@ -66998,7 +66998,7 @@
       </c>
       <c r="H1091" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I1091" t="inlineStr">
@@ -67135,7 +67135,7 @@
       </c>
       <c r="K1093" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L1093" t="inlineStr">
@@ -67185,7 +67185,7 @@
       </c>
       <c r="H1094" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I1094" t="inlineStr">
@@ -67734,7 +67734,7 @@
       </c>
       <c r="H1103" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I1103" t="inlineStr">
@@ -68344,7 +68344,7 @@
       </c>
       <c r="H1113" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I1113" t="inlineStr">
@@ -68405,7 +68405,7 @@
       </c>
       <c r="H1114" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I1114" t="inlineStr">
@@ -68527,7 +68527,7 @@
       </c>
       <c r="H1116" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I1116" t="inlineStr">

--- a/docs/oc-mensuales/articulos-de-aseo-e-higiene/abr-2026.xlsx
+++ b/docs/oc-mensuales/articulos-de-aseo-e-higiene/abr-2026.xlsx
@@ -562,7 +562,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
           <t>USD</t>
@@ -623,7 +627,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
           <t>USD</t>
@@ -684,7 +692,11 @@
           <t>77.806.000-0</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
           <t>USD</t>
@@ -745,7 +757,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr">
         <is>
           <t>USD</t>
@@ -806,7 +822,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr">
         <is>
           <t>USD</t>
@@ -867,7 +887,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr">
         <is>
           <t>USD</t>
@@ -928,7 +952,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr">
         <is>
           <t>USD</t>
@@ -989,7 +1017,11 @@
           <t>77.745.829-9</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1050,7 +1082,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1111,7 +1147,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1233,7 +1273,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1355,7 +1399,11 @@
           <t>78.201.425-0</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1416,7 +1464,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1477,7 +1529,11 @@
           <t>78.209.441-6</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1599,7 +1655,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1660,7 +1720,11 @@
           <t>77.619.564-2</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1721,7 +1785,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1782,7 +1850,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L22" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1904,7 +1976,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L24" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1965,7 +2041,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L25" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2026,7 +2106,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L26" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2087,7 +2171,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L27" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2148,7 +2236,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L28" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2209,7 +2301,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L29" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2270,7 +2366,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L30" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2331,7 +2431,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L31" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2453,7 +2557,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L33" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2514,7 +2622,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L34" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2575,7 +2687,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L35" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2636,7 +2752,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L36" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2697,7 +2817,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L37" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2819,7 +2943,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L39" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2880,7 +3008,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L40" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3002,7 +3134,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L42" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3063,7 +3199,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L43" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3185,7 +3325,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L45" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3246,7 +3390,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr"/>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L46" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3307,7 +3455,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L47" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3429,7 +3581,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr"/>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L49" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3551,7 +3707,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr"/>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L51" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3673,7 +3833,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr"/>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L53" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3734,7 +3898,11 @@
           <t>78.209.499-8</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr"/>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L54" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3795,7 +3963,11 @@
           <t>78.061.716-0</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr"/>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L55" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3856,7 +4028,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr"/>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L56" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3978,7 +4154,11 @@
           <t>76.525.922-3</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr"/>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L58" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4039,7 +4219,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr"/>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L59" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4222,7 +4406,11 @@
           <t>77.717.553-K</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr"/>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L62" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4405,7 +4593,11 @@
           <t>77.478.598-1</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr"/>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L65" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4466,7 +4658,11 @@
           <t>77.478.598-1</t>
         </is>
       </c>
-      <c r="K66" t="inlineStr"/>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L66" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4588,7 +4784,11 @@
           <t>78.209.499-8</t>
         </is>
       </c>
-      <c r="K68" t="inlineStr"/>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L68" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4649,7 +4849,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K69" t="inlineStr"/>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L69" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4710,7 +4914,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K70" t="inlineStr"/>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L70" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4771,7 +4979,11 @@
           <t>77.621.112-5</t>
         </is>
       </c>
-      <c r="K71" t="inlineStr"/>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L71" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4832,7 +5044,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K72" t="inlineStr"/>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L72" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4954,7 +5170,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K74" t="inlineStr"/>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L74" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5015,7 +5235,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K75" t="inlineStr"/>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L75" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5198,7 +5422,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K78" t="inlineStr"/>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L78" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5381,7 +5609,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K81" t="inlineStr"/>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L81" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5503,7 +5735,11 @@
           <t>77.806.000-0</t>
         </is>
       </c>
-      <c r="K83" t="inlineStr"/>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L83" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5686,7 +5922,11 @@
           <t>77.916.035-1</t>
         </is>
       </c>
-      <c r="K86" t="inlineStr"/>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L86" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5747,7 +5987,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K87" t="inlineStr"/>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L87" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5808,7 +6052,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K88" t="inlineStr"/>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L88" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5930,7 +6178,11 @@
           <t>77.649.678-2</t>
         </is>
       </c>
-      <c r="K90" t="inlineStr"/>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L90" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5991,7 +6243,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K91" t="inlineStr"/>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L91" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6174,7 +6430,11 @@
           <t>77.610.393-4</t>
         </is>
       </c>
-      <c r="K94" t="inlineStr"/>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L94" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6235,7 +6495,11 @@
           <t>77.621.112-5</t>
         </is>
       </c>
-      <c r="K95" t="inlineStr"/>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L95" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6296,7 +6560,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K96" t="inlineStr"/>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L96" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6357,7 +6625,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K97" t="inlineStr"/>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L97" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6479,7 +6751,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K99" t="inlineStr"/>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L99" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6601,7 +6877,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K101" t="inlineStr"/>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L101" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6662,7 +6942,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K102" t="inlineStr"/>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L102" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6723,7 +7007,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K103" t="inlineStr"/>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L103" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6967,7 +7255,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K107" t="inlineStr"/>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L107" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7028,7 +7320,11 @@
           <t>78.209.499-8</t>
         </is>
       </c>
-      <c r="K108" t="inlineStr"/>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L108" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7089,7 +7385,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K109" t="inlineStr"/>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L109" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7211,7 +7511,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K111" t="inlineStr"/>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L111" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7333,7 +7637,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K113" t="inlineStr"/>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L113" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7455,7 +7763,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K115" t="inlineStr"/>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L115" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7577,7 +7889,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K117" t="inlineStr"/>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L117" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7638,7 +7954,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K118" t="inlineStr"/>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L118" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7760,7 +8080,11 @@
           <t>78.209.499-8</t>
         </is>
       </c>
-      <c r="K120" t="inlineStr"/>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L120" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7947,7 +8271,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K123" t="inlineStr"/>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L123" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8008,7 +8336,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K124" t="inlineStr"/>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L124" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8069,7 +8401,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K125" t="inlineStr"/>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L125" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8130,7 +8466,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K126" t="inlineStr"/>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L126" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8191,7 +8531,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K127" t="inlineStr"/>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L127" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8252,7 +8596,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K128" t="inlineStr"/>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L128" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8374,7 +8722,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K130" t="inlineStr"/>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L130" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8435,7 +8787,11 @@
           <t>77.045.877-3</t>
         </is>
       </c>
-      <c r="K131" t="inlineStr"/>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L131" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8496,7 +8852,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K132" t="inlineStr"/>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L132" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8557,7 +8917,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K133" t="inlineStr"/>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L133" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8618,7 +8982,11 @@
           <t>78.209.481-5</t>
         </is>
       </c>
-      <c r="K134" t="inlineStr"/>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L134" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8679,7 +9047,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K135" t="inlineStr"/>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L135" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8740,7 +9112,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K136" t="inlineStr"/>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L136" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8984,7 +9360,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K140" t="inlineStr"/>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L140" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9106,7 +9486,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K142" t="inlineStr"/>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L142" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9228,7 +9612,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K144" t="inlineStr"/>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L144" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9289,7 +9677,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K145" t="inlineStr"/>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L145" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9411,7 +9803,11 @@
           <t>78.209.499-8</t>
         </is>
       </c>
-      <c r="K147" t="inlineStr"/>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L147" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9533,7 +9929,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K149" t="inlineStr"/>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L149" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9594,7 +9994,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K150" t="inlineStr"/>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L150" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9716,7 +10120,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K152" t="inlineStr"/>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L152" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9777,7 +10185,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K153" t="inlineStr"/>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L153" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9838,7 +10250,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K154" t="inlineStr"/>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L154" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10021,7 +10437,11 @@
           <t>77.082.051-0</t>
         </is>
       </c>
-      <c r="K157" t="inlineStr"/>
+      <c r="K157" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L157" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10204,7 +10624,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K160" t="inlineStr"/>
+      <c r="K160" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L160" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10326,7 +10750,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K162" t="inlineStr"/>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L162" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10448,7 +10876,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K164" t="inlineStr"/>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L164" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10509,7 +10941,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K165" t="inlineStr"/>
+      <c r="K165" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L165" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10570,7 +11006,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K166" t="inlineStr"/>
+      <c r="K166" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L166" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10753,7 +11193,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K169" t="inlineStr"/>
+      <c r="K169" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L169" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10814,7 +11258,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K170" t="inlineStr"/>
+      <c r="K170" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L170" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10875,7 +11323,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K171" t="inlineStr"/>
+      <c r="K171" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L171" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10936,7 +11388,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K172" t="inlineStr"/>
+      <c r="K172" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L172" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10997,7 +11453,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K173" t="inlineStr"/>
+      <c r="K173" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L173" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11180,7 +11640,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K176" t="inlineStr"/>
+      <c r="K176" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L176" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11241,7 +11705,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K177" t="inlineStr"/>
+      <c r="K177" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L177" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11302,7 +11770,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K178" t="inlineStr"/>
+      <c r="K178" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L178" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11363,7 +11835,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K179" t="inlineStr"/>
+      <c r="K179" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L179" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11424,7 +11900,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K180" t="inlineStr"/>
+      <c r="K180" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L180" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11485,7 +11965,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K181" t="inlineStr"/>
+      <c r="K181" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L181" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11546,7 +12030,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K182" t="inlineStr"/>
+      <c r="K182" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L182" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11607,7 +12095,11 @@
           <t>77.649.678-2</t>
         </is>
       </c>
-      <c r="K183" t="inlineStr"/>
+      <c r="K183" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L183" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11912,7 +12404,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K188" t="inlineStr"/>
+      <c r="K188" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L188" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12034,7 +12530,11 @@
           <t>76.100.732-7</t>
         </is>
       </c>
-      <c r="K190" t="inlineStr"/>
+      <c r="K190" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L190" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12156,7 +12656,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K192" t="inlineStr"/>
+      <c r="K192" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L192" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12217,7 +12721,11 @@
           <t>76.100.732-7</t>
         </is>
       </c>
-      <c r="K193" t="inlineStr"/>
+      <c r="K193" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L193" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12339,7 +12847,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K195" t="inlineStr"/>
+      <c r="K195" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L195" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12400,7 +12912,11 @@
           <t>76.556.184-1</t>
         </is>
       </c>
-      <c r="K196" t="inlineStr"/>
+      <c r="K196" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L196" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12461,7 +12977,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K197" t="inlineStr"/>
+      <c r="K197" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L197" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12522,7 +13042,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K198" t="inlineStr"/>
+      <c r="K198" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L198" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12583,7 +13107,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K199" t="inlineStr"/>
+      <c r="K199" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L199" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12644,7 +13172,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K200" t="inlineStr"/>
+      <c r="K200" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L200" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12766,7 +13298,11 @@
           <t>76.525.922-3</t>
         </is>
       </c>
-      <c r="K202" t="inlineStr"/>
+      <c r="K202" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L202" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12827,7 +13363,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K203" t="inlineStr"/>
+      <c r="K203" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L203" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12888,7 +13428,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K204" t="inlineStr"/>
+      <c r="K204" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L204" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12949,7 +13493,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K205" t="inlineStr"/>
+      <c r="K205" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L205" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13010,7 +13558,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K206" t="inlineStr"/>
+      <c r="K206" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L206" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13071,7 +13623,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K207" t="inlineStr"/>
+      <c r="K207" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L207" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13193,7 +13749,11 @@
           <t>78.307.990-9</t>
         </is>
       </c>
-      <c r="K209" t="inlineStr"/>
+      <c r="K209" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L209" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13254,7 +13814,11 @@
           <t>96.989.530-7</t>
         </is>
       </c>
-      <c r="K210" t="inlineStr"/>
+      <c r="K210" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L210" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13376,7 +13940,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K212" t="inlineStr"/>
+      <c r="K212" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L212" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13437,7 +14005,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K213" t="inlineStr"/>
+      <c r="K213" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L213" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13498,7 +14070,11 @@
           <t>77.577.274-3</t>
         </is>
       </c>
-      <c r="K214" t="inlineStr"/>
+      <c r="K214" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L214" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13620,7 +14196,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K216" t="inlineStr"/>
+      <c r="K216" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L216" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13681,7 +14261,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K217" t="inlineStr"/>
+      <c r="K217" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L217" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13742,7 +14326,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K218" t="inlineStr"/>
+      <c r="K218" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L218" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13803,7 +14391,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K219" t="inlineStr"/>
+      <c r="K219" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L219" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13925,7 +14517,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K221" t="inlineStr"/>
+      <c r="K221" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L221" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13986,7 +14582,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K222" t="inlineStr"/>
+      <c r="K222" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L222" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14047,7 +14647,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K223" t="inlineStr"/>
+      <c r="K223" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L223" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14108,7 +14712,11 @@
           <t>76.100.732-7</t>
         </is>
       </c>
-      <c r="K224" t="inlineStr"/>
+      <c r="K224" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L224" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14169,7 +14777,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K225" t="inlineStr"/>
+      <c r="K225" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L225" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14230,7 +14842,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K226" t="inlineStr"/>
+      <c r="K226" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L226" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14291,7 +14907,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K227" t="inlineStr"/>
+      <c r="K227" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L227" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14413,7 +15033,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K229" t="inlineStr"/>
+      <c r="K229" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L229" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14474,7 +15098,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K230" t="inlineStr"/>
+      <c r="K230" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L230" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14596,7 +15224,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K232" t="inlineStr"/>
+      <c r="K232" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L232" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14718,7 +15350,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K234" t="inlineStr"/>
+      <c r="K234" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L234" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14779,7 +15415,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K235" t="inlineStr"/>
+      <c r="K235" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L235" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14840,7 +15480,11 @@
           <t>76.539.061-3</t>
         </is>
       </c>
-      <c r="K236" t="inlineStr"/>
+      <c r="K236" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L236" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14901,7 +15545,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K237" t="inlineStr"/>
+      <c r="K237" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L237" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14962,7 +15610,11 @@
           <t>76.556.184-1</t>
         </is>
       </c>
-      <c r="K238" t="inlineStr"/>
+      <c r="K238" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L238" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15023,7 +15675,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K239" t="inlineStr"/>
+      <c r="K239" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L239" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15084,7 +15740,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K240" t="inlineStr"/>
+      <c r="K240" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L240" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15145,7 +15805,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K241" t="inlineStr"/>
+      <c r="K241" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L241" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15206,7 +15870,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K242" t="inlineStr"/>
+      <c r="K242" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L242" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15267,7 +15935,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K243" t="inlineStr"/>
+      <c r="K243" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L243" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15328,7 +16000,11 @@
           <t>78.212.867-1</t>
         </is>
       </c>
-      <c r="K244" t="inlineStr"/>
+      <c r="K244" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L244" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15389,7 +16065,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K245" t="inlineStr"/>
+      <c r="K245" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L245" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15450,7 +16130,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K246" t="inlineStr"/>
+      <c r="K246" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L246" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15511,7 +16195,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K247" t="inlineStr"/>
+      <c r="K247" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L247" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15572,7 +16260,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K248" t="inlineStr"/>
+      <c r="K248" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L248" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15694,7 +16386,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K250" t="inlineStr"/>
+      <c r="K250" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L250" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15938,7 +16634,11 @@
           <t>77.909.444-8</t>
         </is>
       </c>
-      <c r="K254" t="inlineStr"/>
+      <c r="K254" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L254" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16060,7 +16760,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K256" t="inlineStr"/>
+      <c r="K256" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L256" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16121,7 +16825,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K257" t="inlineStr"/>
+      <c r="K257" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L257" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16243,7 +16951,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K259" t="inlineStr"/>
+      <c r="K259" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L259" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16304,7 +17016,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K260" t="inlineStr"/>
+      <c r="K260" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L260" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16365,7 +17081,11 @@
           <t>77.720.988-4</t>
         </is>
       </c>
-      <c r="K261" t="inlineStr"/>
+      <c r="K261" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L261" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16426,7 +17146,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K262" t="inlineStr"/>
+      <c r="K262" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L262" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16487,7 +17211,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K263" t="inlineStr"/>
+      <c r="K263" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L263" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16548,7 +17276,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K264" t="inlineStr"/>
+      <c r="K264" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L264" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16609,7 +17341,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K265" t="inlineStr"/>
+      <c r="K265" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L265" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16731,7 +17467,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K267" t="inlineStr"/>
+      <c r="K267" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L267" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16792,7 +17532,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K268" t="inlineStr"/>
+      <c r="K268" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L268" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16853,7 +17597,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K269" t="inlineStr"/>
+      <c r="K269" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L269" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16914,7 +17662,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K270" t="inlineStr"/>
+      <c r="K270" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L270" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16975,7 +17727,11 @@
           <t>76.817.360-5</t>
         </is>
       </c>
-      <c r="K271" t="inlineStr"/>
+      <c r="K271" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L271" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17036,7 +17792,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K272" t="inlineStr"/>
+      <c r="K272" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L272" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17097,7 +17857,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K273" t="inlineStr"/>
+      <c r="K273" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L273" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17158,7 +17922,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K274" t="inlineStr"/>
+      <c r="K274" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L274" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17219,7 +17987,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K275" t="inlineStr"/>
+      <c r="K275" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L275" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17280,7 +18052,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K276" t="inlineStr"/>
+      <c r="K276" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L276" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17402,7 +18178,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K278" t="inlineStr"/>
+      <c r="K278" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L278" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17463,7 +18243,11 @@
           <t>78.209.499-8</t>
         </is>
       </c>
-      <c r="K279" t="inlineStr"/>
+      <c r="K279" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L279" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17524,7 +18308,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K280" t="inlineStr"/>
+      <c r="K280" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L280" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17585,7 +18373,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K281" t="inlineStr"/>
+      <c r="K281" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L281" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17768,7 +18560,11 @@
           <t>77.934.122-4</t>
         </is>
       </c>
-      <c r="K284" t="inlineStr"/>
+      <c r="K284" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L284" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17829,7 +18625,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K285" t="inlineStr"/>
+      <c r="K285" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L285" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17890,7 +18690,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K286" t="inlineStr"/>
+      <c r="K286" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L286" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17951,7 +18755,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K287" t="inlineStr"/>
+      <c r="K287" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L287" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18073,7 +18881,11 @@
           <t>78.209.499-8</t>
         </is>
       </c>
-      <c r="K289" t="inlineStr"/>
+      <c r="K289" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L289" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18134,7 +18946,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K290" t="inlineStr"/>
+      <c r="K290" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L290" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18195,7 +19011,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K291" t="inlineStr"/>
+      <c r="K291" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L291" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18256,7 +19076,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K292" t="inlineStr"/>
+      <c r="K292" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L292" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18317,7 +19141,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K293" t="inlineStr"/>
+      <c r="K293" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L293" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18378,7 +19206,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K294" t="inlineStr"/>
+      <c r="K294" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L294" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18683,7 +19515,11 @@
           <t>77.529.681-K</t>
         </is>
       </c>
-      <c r="K299" t="inlineStr"/>
+      <c r="K299" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L299" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18744,7 +19580,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K300" t="inlineStr"/>
+      <c r="K300" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L300" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19049,7 +19889,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K305" t="inlineStr"/>
+      <c r="K305" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L305" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19110,7 +19954,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K306" t="inlineStr"/>
+      <c r="K306" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L306" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19171,7 +20019,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K307" t="inlineStr"/>
+      <c r="K307" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L307" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19232,7 +20084,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K308" t="inlineStr"/>
+      <c r="K308" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L308" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19415,7 +20271,11 @@
           <t>76.556.184-1</t>
         </is>
       </c>
-      <c r="K311" t="inlineStr"/>
+      <c r="K311" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L311" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19476,7 +20336,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K312" t="inlineStr"/>
+      <c r="K312" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L312" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19537,7 +20401,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K313" t="inlineStr"/>
+      <c r="K313" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L313" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19598,7 +20466,11 @@
           <t>77.610.393-4</t>
         </is>
       </c>
-      <c r="K314" t="inlineStr"/>
+      <c r="K314" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L314" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19720,7 +20592,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K316" t="inlineStr"/>
+      <c r="K316" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L316" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19781,7 +20657,11 @@
           <t>76.556.184-1</t>
         </is>
       </c>
-      <c r="K317" t="inlineStr"/>
+      <c r="K317" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L317" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19842,7 +20722,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K318" t="inlineStr"/>
+      <c r="K318" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L318" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19903,7 +20787,11 @@
           <t>78.007.139-7</t>
         </is>
       </c>
-      <c r="K319" t="inlineStr"/>
+      <c r="K319" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L319" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19964,7 +20852,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K320" t="inlineStr"/>
+      <c r="K320" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L320" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20147,7 +21039,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K323" t="inlineStr"/>
+      <c r="K323" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L323" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20208,7 +21104,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K324" t="inlineStr"/>
+      <c r="K324" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L324" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20269,7 +21169,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K325" t="inlineStr"/>
+      <c r="K325" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L325" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20330,7 +21234,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K326" t="inlineStr"/>
+      <c r="K326" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L326" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20391,7 +21299,11 @@
           <t>78.307.990-9</t>
         </is>
       </c>
-      <c r="K327" t="inlineStr"/>
+      <c r="K327" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L327" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20513,7 +21425,11 @@
           <t>78.209.481-5</t>
         </is>
       </c>
-      <c r="K329" t="inlineStr"/>
+      <c r="K329" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L329" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20696,7 +21612,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K332" t="inlineStr"/>
+      <c r="K332" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L332" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20757,7 +21677,11 @@
           <t>78.209.441-6</t>
         </is>
       </c>
-      <c r="K333" t="inlineStr"/>
+      <c r="K333" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L333" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20818,7 +21742,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K334" t="inlineStr"/>
+      <c r="K334" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L334" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20879,7 +21807,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K335" t="inlineStr"/>
+      <c r="K335" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L335" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21001,7 +21933,11 @@
           <t>78.307.990-9</t>
         </is>
       </c>
-      <c r="K337" t="inlineStr"/>
+      <c r="K337" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L337" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21123,7 +22059,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K339" t="inlineStr"/>
+      <c r="K339" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L339" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21306,7 +22246,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K342" t="inlineStr"/>
+      <c r="K342" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L342" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21428,7 +22372,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K344" t="inlineStr"/>
+      <c r="K344" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L344" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21672,7 +22620,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K348" t="inlineStr"/>
+      <c r="K348" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L348" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21855,7 +22807,11 @@
           <t>78.061.716-0</t>
         </is>
       </c>
-      <c r="K351" t="inlineStr"/>
+      <c r="K351" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L351" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22038,7 +22994,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K354" t="inlineStr"/>
+      <c r="K354" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L354" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22282,7 +23242,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K358" t="inlineStr"/>
+      <c r="K358" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L358" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22526,7 +23490,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K362" t="inlineStr"/>
+      <c r="K362" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L362" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22587,7 +23555,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K363" t="inlineStr"/>
+      <c r="K363" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L363" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22713,7 +23685,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K365" t="inlineStr"/>
+      <c r="K365" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L365" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22900,7 +23876,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K368" t="inlineStr"/>
+      <c r="K368" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L368" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23022,7 +24002,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K370" t="inlineStr"/>
+      <c r="K370" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L370" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23083,7 +24067,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K371" t="inlineStr"/>
+      <c r="K371" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L371" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23392,7 +24380,11 @@
           <t>77.393.702-8</t>
         </is>
       </c>
-      <c r="K376" t="inlineStr"/>
+      <c r="K376" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L376" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23453,7 +24445,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K377" t="inlineStr"/>
+      <c r="K377" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L377" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23514,7 +24510,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K378" t="inlineStr"/>
+      <c r="K378" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L378" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23575,7 +24575,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K379" t="inlineStr"/>
+      <c r="K379" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L379" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23636,7 +24640,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K380" t="inlineStr"/>
+      <c r="K380" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L380" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23697,7 +24705,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K381" t="inlineStr"/>
+      <c r="K381" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L381" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23758,7 +24770,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K382" t="inlineStr"/>
+      <c r="K382" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L382" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23941,7 +24957,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K385" t="inlineStr"/>
+      <c r="K385" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L385" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24063,7 +25083,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K387" t="inlineStr"/>
+      <c r="K387" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L387" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24185,7 +25209,11 @@
           <t>78.212.867-1</t>
         </is>
       </c>
-      <c r="K389" t="inlineStr"/>
+      <c r="K389" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L389" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24246,7 +25274,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K390" t="inlineStr"/>
+      <c r="K390" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L390" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24368,7 +25400,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K392" t="inlineStr"/>
+      <c r="K392" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L392" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24490,7 +25526,11 @@
           <t>77.249.249-9</t>
         </is>
       </c>
-      <c r="K394" t="inlineStr"/>
+      <c r="K394" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L394" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24551,7 +25591,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K395" t="inlineStr"/>
+      <c r="K395" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L395" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24612,7 +25656,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K396" t="inlineStr"/>
+      <c r="K396" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L396" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24673,7 +25721,11 @@
           <t>77.927.120-K</t>
         </is>
       </c>
-      <c r="K397" t="inlineStr"/>
+      <c r="K397" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L397" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24795,7 +25847,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K399" t="inlineStr"/>
+      <c r="K399" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L399" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24917,7 +25973,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K401" t="inlineStr"/>
+      <c r="K401" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L401" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25039,7 +26099,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K403" t="inlineStr"/>
+      <c r="K403" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L403" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25100,7 +26164,11 @@
           <t>77.499.324-K</t>
         </is>
       </c>
-      <c r="K404" t="inlineStr"/>
+      <c r="K404" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L404" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25161,7 +26229,11 @@
           <t>77.720.988-4</t>
         </is>
       </c>
-      <c r="K405" t="inlineStr"/>
+      <c r="K405" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L405" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25222,7 +26294,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K406" t="inlineStr"/>
+      <c r="K406" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L406" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25344,7 +26420,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K408" t="inlineStr"/>
+      <c r="K408" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L408" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25405,7 +26485,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K409" t="inlineStr"/>
+      <c r="K409" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L409" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25466,7 +26550,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K410" t="inlineStr"/>
+      <c r="K410" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L410" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25527,7 +26615,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K411" t="inlineStr"/>
+      <c r="K411" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L411" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25710,7 +26802,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K414" t="inlineStr"/>
+      <c r="K414" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L414" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25832,7 +26928,11 @@
           <t>78.307.990-9</t>
         </is>
       </c>
-      <c r="K416" t="inlineStr"/>
+      <c r="K416" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L416" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25893,7 +26993,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K417" t="inlineStr"/>
+      <c r="K417" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L417" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25954,7 +27058,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K418" t="inlineStr"/>
+      <c r="K418" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L418" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26015,7 +27123,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K419" t="inlineStr"/>
+      <c r="K419" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L419" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26137,7 +27249,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K421" t="inlineStr"/>
+      <c r="K421" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L421" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26320,7 +27436,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K424" t="inlineStr"/>
+      <c r="K424" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L424" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26381,7 +27501,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K425" t="inlineStr"/>
+      <c r="K425" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L425" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26442,7 +27566,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K426" t="inlineStr"/>
+      <c r="K426" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L426" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26503,7 +27631,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K427" t="inlineStr"/>
+      <c r="K427" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L427" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26625,7 +27757,11 @@
           <t>77.745.829-9</t>
         </is>
       </c>
-      <c r="K429" t="inlineStr"/>
+      <c r="K429" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L429" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26747,7 +27883,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K431" t="inlineStr"/>
+      <c r="K431" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L431" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26808,7 +27948,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K432" t="inlineStr"/>
+      <c r="K432" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L432" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26869,7 +28013,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K433" t="inlineStr"/>
+      <c r="K433" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L433" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26930,7 +28078,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K434" t="inlineStr"/>
+      <c r="K434" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L434" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26991,7 +28143,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K435" t="inlineStr"/>
+      <c r="K435" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L435" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27052,7 +28208,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K436" t="inlineStr"/>
+      <c r="K436" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L436" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27113,7 +28273,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K437" t="inlineStr"/>
+      <c r="K437" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L437" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27174,7 +28338,11 @@
           <t>77.610.393-4</t>
         </is>
       </c>
-      <c r="K438" t="inlineStr"/>
+      <c r="K438" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L438" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27235,7 +28403,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K439" t="inlineStr"/>
+      <c r="K439" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L439" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27296,7 +28468,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K440" t="inlineStr"/>
+      <c r="K440" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L440" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27418,7 +28594,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K442" t="inlineStr"/>
+      <c r="K442" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L442" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27479,7 +28659,11 @@
           <t>78.212.867-1</t>
         </is>
       </c>
-      <c r="K443" t="inlineStr"/>
+      <c r="K443" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L443" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27540,7 +28724,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K444" t="inlineStr"/>
+      <c r="K444" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L444" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27601,7 +28789,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K445" t="inlineStr"/>
+      <c r="K445" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L445" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27662,7 +28854,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K446" t="inlineStr"/>
+      <c r="K446" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L446" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27723,7 +28919,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K447" t="inlineStr"/>
+      <c r="K447" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L447" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27845,7 +29045,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K449" t="inlineStr"/>
+      <c r="K449" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L449" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27906,7 +29110,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K450" t="inlineStr"/>
+      <c r="K450" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L450" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27967,7 +29175,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K451" t="inlineStr"/>
+      <c r="K451" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L451" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28089,7 +29301,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K453" t="inlineStr"/>
+      <c r="K453" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L453" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28150,7 +29366,11 @@
           <t>77.362.622-7</t>
         </is>
       </c>
-      <c r="K454" t="inlineStr"/>
+      <c r="K454" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L454" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28211,7 +29431,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K455" t="inlineStr"/>
+      <c r="K455" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L455" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28455,7 +29679,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K459" t="inlineStr"/>
+      <c r="K459" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L459" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28577,7 +29805,11 @@
           <t>77.478.598-1</t>
         </is>
       </c>
-      <c r="K461" t="inlineStr"/>
+      <c r="K461" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L461" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28638,7 +29870,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K462" t="inlineStr"/>
+      <c r="K462" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L462" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28699,7 +29935,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K463" t="inlineStr"/>
+      <c r="K463" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L463" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28760,7 +30000,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K464" t="inlineStr"/>
+      <c r="K464" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L464" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28821,7 +30065,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K465" t="inlineStr"/>
+      <c r="K465" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L465" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28882,7 +30130,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K466" t="inlineStr"/>
+      <c r="K466" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L466" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28943,7 +30195,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K467" t="inlineStr"/>
+      <c r="K467" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L467" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29004,7 +30260,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K468" t="inlineStr"/>
+      <c r="K468" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L468" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29065,7 +30325,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K469" t="inlineStr"/>
+      <c r="K469" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L469" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29248,7 +30512,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K472" t="inlineStr"/>
+      <c r="K472" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L472" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29370,7 +30638,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K474" t="inlineStr"/>
+      <c r="K474" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L474" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29431,7 +30703,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K475" t="inlineStr"/>
+      <c r="K475" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L475" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29553,7 +30829,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K477" t="inlineStr"/>
+      <c r="K477" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L477" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29614,7 +30894,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K478" t="inlineStr"/>
+      <c r="K478" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L478" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29675,7 +30959,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K479" t="inlineStr"/>
+      <c r="K479" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L479" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29797,7 +31085,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K481" t="inlineStr"/>
+      <c r="K481" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L481" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29919,7 +31211,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K483" t="inlineStr"/>
+      <c r="K483" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L483" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29980,7 +31276,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K484" t="inlineStr"/>
+      <c r="K484" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L484" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30102,7 +31402,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K486" t="inlineStr"/>
+      <c r="K486" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L486" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30163,7 +31467,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K487" t="inlineStr"/>
+      <c r="K487" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L487" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30224,7 +31532,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K488" t="inlineStr"/>
+      <c r="K488" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L488" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30407,7 +31719,11 @@
           <t>77.621.112-5</t>
         </is>
       </c>
-      <c r="K491" t="inlineStr"/>
+      <c r="K491" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L491" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30468,7 +31784,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K492" t="inlineStr"/>
+      <c r="K492" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L492" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30590,7 +31910,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K494" t="inlineStr"/>
+      <c r="K494" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L494" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30651,7 +31975,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K495" t="inlineStr"/>
+      <c r="K495" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L495" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30773,7 +32101,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K497" t="inlineStr"/>
+      <c r="K497" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L497" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30834,7 +32166,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K498" t="inlineStr"/>
+      <c r="K498" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L498" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30895,7 +32231,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K499" t="inlineStr"/>
+      <c r="K499" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L499" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30956,7 +32296,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K500" t="inlineStr"/>
+      <c r="K500" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L500" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31017,7 +32361,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K501" t="inlineStr"/>
+      <c r="K501" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L501" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31261,7 +32609,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K505" t="inlineStr"/>
+      <c r="K505" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L505" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31322,7 +32674,11 @@
           <t>78.061.716-0</t>
         </is>
       </c>
-      <c r="K506" t="inlineStr"/>
+      <c r="K506" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L506" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31383,7 +32739,11 @@
           <t>77.619.564-2</t>
         </is>
       </c>
-      <c r="K507" t="inlineStr"/>
+      <c r="K507" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L507" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31505,7 +32865,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K509" t="inlineStr"/>
+      <c r="K509" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L509" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31627,7 +32991,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K511" t="inlineStr"/>
+      <c r="K511" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L511" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31688,7 +33056,11 @@
           <t>79.722.860-5</t>
         </is>
       </c>
-      <c r="K512" t="inlineStr"/>
+      <c r="K512" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L512" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31810,7 +33182,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K514" t="inlineStr"/>
+      <c r="K514" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L514" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31932,7 +33308,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K516" t="inlineStr"/>
+      <c r="K516" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L516" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31993,7 +33373,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K517" t="inlineStr"/>
+      <c r="K517" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L517" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32115,7 +33499,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K519" t="inlineStr"/>
+      <c r="K519" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L519" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32237,7 +33625,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K521" t="inlineStr"/>
+      <c r="K521" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L521" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32298,7 +33690,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K522" t="inlineStr"/>
+      <c r="K522" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L522" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32359,7 +33755,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K523" t="inlineStr"/>
+      <c r="K523" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L523" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32542,7 +33942,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K526" t="inlineStr"/>
+      <c r="K526" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L526" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32603,7 +34007,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K527" t="inlineStr"/>
+      <c r="K527" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L527" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32847,7 +34255,11 @@
           <t>76.556.184-1</t>
         </is>
       </c>
-      <c r="K531" t="inlineStr"/>
+      <c r="K531" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L531" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32969,7 +34381,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K533" t="inlineStr"/>
+      <c r="K533" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L533" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33091,7 +34507,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K535" t="inlineStr"/>
+      <c r="K535" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L535" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33152,7 +34572,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K536" t="inlineStr"/>
+      <c r="K536" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L536" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33213,7 +34637,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K537" t="inlineStr"/>
+      <c r="K537" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L537" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33457,7 +34885,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K541" t="inlineStr"/>
+      <c r="K541" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L541" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33518,7 +34950,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K542" t="inlineStr"/>
+      <c r="K542" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L542" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33579,7 +35015,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K543" t="inlineStr"/>
+      <c r="K543" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L543" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33640,7 +35080,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K544" t="inlineStr"/>
+      <c r="K544" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L544" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33701,7 +35145,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K545" t="inlineStr"/>
+      <c r="K545" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L545" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33762,7 +35210,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K546" t="inlineStr"/>
+      <c r="K546" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L546" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33823,7 +35275,11 @@
           <t>77.621.112-5</t>
         </is>
       </c>
-      <c r="K547" t="inlineStr"/>
+      <c r="K547" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L547" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33884,7 +35340,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K548" t="inlineStr"/>
+      <c r="K548" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L548" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34067,7 +35527,11 @@
           <t>77.499.324-K</t>
         </is>
       </c>
-      <c r="K551" t="inlineStr"/>
+      <c r="K551" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L551" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34128,7 +35592,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K552" t="inlineStr"/>
+      <c r="K552" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L552" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34189,7 +35657,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K553" t="inlineStr"/>
+      <c r="K553" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L553" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34311,7 +35783,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K555" t="inlineStr"/>
+      <c r="K555" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L555" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34372,7 +35848,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K556" t="inlineStr"/>
+      <c r="K556" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L556" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34555,7 +36035,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K559" t="inlineStr"/>
+      <c r="K559" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L559" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34677,7 +36161,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K561" t="inlineStr"/>
+      <c r="K561" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L561" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34738,7 +36226,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K562" t="inlineStr"/>
+      <c r="K562" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L562" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34799,7 +36291,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K563" t="inlineStr"/>
+      <c r="K563" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L563" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34982,7 +36478,11 @@
           <t>78.209.441-6</t>
         </is>
       </c>
-      <c r="K566" t="inlineStr"/>
+      <c r="K566" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L566" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35043,7 +36543,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K567" t="inlineStr"/>
+      <c r="K567" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L567" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35104,7 +36608,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K568" t="inlineStr"/>
+      <c r="K568" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L568" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35165,7 +36673,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K569" t="inlineStr"/>
+      <c r="K569" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L569" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35226,7 +36738,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K570" t="inlineStr"/>
+      <c r="K570" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L570" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35287,7 +36803,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K571" t="inlineStr"/>
+      <c r="K571" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L571" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35348,7 +36868,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K572" t="inlineStr"/>
+      <c r="K572" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L572" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35592,7 +37116,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K576" t="inlineStr"/>
+      <c r="K576" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L576" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35714,7 +37242,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K578" t="inlineStr"/>
+      <c r="K578" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L578" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35775,7 +37307,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K579" t="inlineStr"/>
+      <c r="K579" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L579" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35836,7 +37372,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K580" t="inlineStr"/>
+      <c r="K580" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L580" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35897,7 +37437,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K581" t="inlineStr"/>
+      <c r="K581" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L581" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35958,7 +37502,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K582" t="inlineStr"/>
+      <c r="K582" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L582" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36080,7 +37628,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K584" t="inlineStr"/>
+      <c r="K584" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L584" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36141,7 +37693,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K585" t="inlineStr"/>
+      <c r="K585" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L585" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36263,7 +37819,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K587" t="inlineStr"/>
+      <c r="K587" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L587" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36324,7 +37884,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K588" t="inlineStr"/>
+      <c r="K588" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L588" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36385,7 +37949,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K589" t="inlineStr"/>
+      <c r="K589" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L589" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36446,7 +38014,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K590" t="inlineStr"/>
+      <c r="K590" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L590" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36507,7 +38079,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K591" t="inlineStr"/>
+      <c r="K591" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L591" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36568,7 +38144,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K592" t="inlineStr"/>
+      <c r="K592" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L592" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36690,7 +38270,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K594" t="inlineStr"/>
+      <c r="K594" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L594" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36751,7 +38335,11 @@
           <t>78.209.441-6</t>
         </is>
       </c>
-      <c r="K595" t="inlineStr"/>
+      <c r="K595" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L595" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36812,7 +38400,11 @@
           <t>78.209.441-6</t>
         </is>
       </c>
-      <c r="K596" t="inlineStr"/>
+      <c r="K596" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L596" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36873,7 +38465,11 @@
           <t>78.209.441-6</t>
         </is>
       </c>
-      <c r="K597" t="inlineStr"/>
+      <c r="K597" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L597" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36934,7 +38530,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K598" t="inlineStr"/>
+      <c r="K598" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L598" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36995,7 +38595,11 @@
           <t>78.209.441-6</t>
         </is>
       </c>
-      <c r="K599" t="inlineStr"/>
+      <c r="K599" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L599" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37056,7 +38660,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K600" t="inlineStr"/>
+      <c r="K600" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L600" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37300,7 +38908,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K604" t="inlineStr"/>
+      <c r="K604" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L604" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37361,7 +38973,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K605" t="inlineStr"/>
+      <c r="K605" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L605" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37422,7 +39038,11 @@
           <t>77.577.274-3</t>
         </is>
       </c>
-      <c r="K606" t="inlineStr"/>
+      <c r="K606" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L606" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37483,7 +39103,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K607" t="inlineStr"/>
+      <c r="K607" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L607" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37544,7 +39168,11 @@
           <t>77.649.678-2</t>
         </is>
       </c>
-      <c r="K608" t="inlineStr"/>
+      <c r="K608" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L608" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37605,7 +39233,11 @@
           <t>77.478.598-1</t>
         </is>
       </c>
-      <c r="K609" t="inlineStr"/>
+      <c r="K609" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L609" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37666,7 +39298,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K610" t="inlineStr"/>
+      <c r="K610" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L610" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37727,7 +39363,11 @@
           <t>76.317.833-1</t>
         </is>
       </c>
-      <c r="K611" t="inlineStr"/>
+      <c r="K611" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L611" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38032,7 +39672,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K616" t="inlineStr"/>
+      <c r="K616" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L616" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38093,7 +39737,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K617" t="inlineStr"/>
+      <c r="K617" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L617" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38154,7 +39802,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K618" t="inlineStr"/>
+      <c r="K618" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L618" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38215,7 +39867,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K619" t="inlineStr"/>
+      <c r="K619" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L619" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38276,7 +39932,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K620" t="inlineStr"/>
+      <c r="K620" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L620" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38337,7 +39997,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K621" t="inlineStr"/>
+      <c r="K621" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L621" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38520,7 +40184,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K624" t="inlineStr"/>
+      <c r="K624" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L624" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38581,7 +40249,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K625" t="inlineStr"/>
+      <c r="K625" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L625" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38642,7 +40314,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K626" t="inlineStr"/>
+      <c r="K626" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L626" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38764,7 +40440,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K628" t="inlineStr"/>
+      <c r="K628" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L628" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38825,7 +40505,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K629" t="inlineStr"/>
+      <c r="K629" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L629" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38886,7 +40570,11 @@
           <t>79.722.860-5</t>
         </is>
       </c>
-      <c r="K630" t="inlineStr"/>
+      <c r="K630" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L630" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39008,7 +40696,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K632" t="inlineStr"/>
+      <c r="K632" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L632" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39130,7 +40822,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K634" t="inlineStr"/>
+      <c r="K634" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L634" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39191,7 +40887,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K635" t="inlineStr"/>
+      <c r="K635" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L635" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39313,7 +41013,11 @@
           <t>77.934.122-4</t>
         </is>
       </c>
-      <c r="K637" t="inlineStr"/>
+      <c r="K637" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L637" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39622,7 +41326,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K642" t="inlineStr"/>
+      <c r="K642" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L642" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39683,7 +41391,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K643" t="inlineStr"/>
+      <c r="K643" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L643" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39866,7 +41578,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K646" t="inlineStr"/>
+      <c r="K646" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L646" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39927,7 +41643,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K647" t="inlineStr"/>
+      <c r="K647" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L647" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39988,7 +41708,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K648" t="inlineStr"/>
+      <c r="K648" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L648" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40110,7 +41834,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K650" t="inlineStr"/>
+      <c r="K650" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L650" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40171,7 +41899,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K651" t="inlineStr"/>
+      <c r="K651" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L651" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40232,7 +41964,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K652" t="inlineStr"/>
+      <c r="K652" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L652" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40354,7 +42090,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K654" t="inlineStr"/>
+      <c r="K654" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L654" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40415,7 +42155,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K655" t="inlineStr"/>
+      <c r="K655" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L655" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40476,7 +42220,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K656" t="inlineStr"/>
+      <c r="K656" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L656" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40537,7 +42285,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K657" t="inlineStr"/>
+      <c r="K657" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L657" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40598,7 +42350,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K658" t="inlineStr"/>
+      <c r="K658" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L658" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40720,7 +42476,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K660" t="inlineStr"/>
+      <c r="K660" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L660" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40781,7 +42541,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K661" t="inlineStr"/>
+      <c r="K661" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L661" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40964,7 +42728,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K664" t="inlineStr"/>
+      <c r="K664" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L664" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41025,7 +42793,11 @@
           <t>77.806.000-0</t>
         </is>
       </c>
-      <c r="K665" t="inlineStr"/>
+      <c r="K665" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L665" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41086,7 +42858,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K666" t="inlineStr"/>
+      <c r="K666" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L666" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41147,7 +42923,11 @@
           <t>78.209.481-5</t>
         </is>
       </c>
-      <c r="K667" t="inlineStr"/>
+      <c r="K667" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L667" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41269,7 +43049,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K669" t="inlineStr"/>
+      <c r="K669" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L669" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41330,7 +43114,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K670" t="inlineStr"/>
+      <c r="K670" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L670" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41391,7 +43179,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K671" t="inlineStr"/>
+      <c r="K671" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L671" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41574,7 +43366,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K674" t="inlineStr"/>
+      <c r="K674" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L674" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41635,7 +43431,11 @@
           <t>76.100.732-7</t>
         </is>
       </c>
-      <c r="K675" t="inlineStr"/>
+      <c r="K675" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L675" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41696,7 +43496,11 @@
           <t>78.209.499-8</t>
         </is>
       </c>
-      <c r="K676" t="inlineStr"/>
+      <c r="K676" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L676" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41757,7 +43561,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K677" t="inlineStr"/>
+      <c r="K677" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L677" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41818,7 +43626,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K678" t="inlineStr"/>
+      <c r="K678" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L678" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41879,7 +43691,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K679" t="inlineStr"/>
+      <c r="K679" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L679" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41940,7 +43756,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K680" t="inlineStr"/>
+      <c r="K680" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L680" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42001,7 +43821,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K681" t="inlineStr"/>
+      <c r="K681" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L681" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42062,7 +43886,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K682" t="inlineStr"/>
+      <c r="K682" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L682" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42123,7 +43951,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K683" t="inlineStr"/>
+      <c r="K683" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L683" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42184,7 +44016,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K684" t="inlineStr"/>
+      <c r="K684" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L684" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42428,7 +44264,11 @@
           <t>78.212.867-1</t>
         </is>
       </c>
-      <c r="K688" t="inlineStr"/>
+      <c r="K688" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L688" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42611,7 +44451,11 @@
           <t>78.212.867-1</t>
         </is>
       </c>
-      <c r="K691" t="inlineStr"/>
+      <c r="K691" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L691" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42672,7 +44516,11 @@
           <t>78.203.286-0</t>
         </is>
       </c>
-      <c r="K692" t="inlineStr"/>
+      <c r="K692" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L692" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42733,7 +44581,11 @@
           <t>77.909.208-9</t>
         </is>
       </c>
-      <c r="K693" t="inlineStr"/>
+      <c r="K693" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L693" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42794,7 +44646,11 @@
           <t>76.715.074-1</t>
         </is>
       </c>
-      <c r="K694" t="inlineStr"/>
+      <c r="K694" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L694" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42855,7 +44711,11 @@
           <t>77.621.112-5</t>
         </is>
       </c>
-      <c r="K695" t="inlineStr"/>
+      <c r="K695" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L695" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42916,7 +44776,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K696" t="inlineStr"/>
+      <c r="K696" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L696" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42977,7 +44841,11 @@
           <t>77.499.324-K</t>
         </is>
       </c>
-      <c r="K697" t="inlineStr"/>
+      <c r="K697" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L697" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43099,7 +44967,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K699" t="inlineStr"/>
+      <c r="K699" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L699" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43221,7 +45093,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K701" t="inlineStr"/>
+      <c r="K701" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L701" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43282,7 +45158,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K702" t="inlineStr"/>
+      <c r="K702" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L702" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43343,7 +45223,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K703" t="inlineStr"/>
+      <c r="K703" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L703" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43465,7 +45349,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K705" t="inlineStr"/>
+      <c r="K705" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L705" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43526,7 +45414,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K706" t="inlineStr"/>
+      <c r="K706" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L706" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43587,7 +45479,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K707" t="inlineStr"/>
+      <c r="K707" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L707" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43709,7 +45605,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K709" t="inlineStr"/>
+      <c r="K709" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L709" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43770,7 +45670,11 @@
           <t>78.209.481-5</t>
         </is>
       </c>
-      <c r="K710" t="inlineStr"/>
+      <c r="K710" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L710" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43831,7 +45735,11 @@
           <t>76.556.184-1</t>
         </is>
       </c>
-      <c r="K711" t="inlineStr"/>
+      <c r="K711" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L711" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43892,7 +45800,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K712" t="inlineStr"/>
+      <c r="K712" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L712" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44014,7 +45926,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K714" t="inlineStr"/>
+      <c r="K714" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L714" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44075,7 +45991,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K715" t="inlineStr"/>
+      <c r="K715" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L715" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44319,7 +46239,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K719" t="inlineStr"/>
+      <c r="K719" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L719" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44502,7 +46426,11 @@
           <t>77.621.112-5</t>
         </is>
       </c>
-      <c r="K722" t="inlineStr"/>
+      <c r="K722" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L722" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44624,7 +46552,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K724" t="inlineStr"/>
+      <c r="K724" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L724" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44685,7 +46617,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K725" t="inlineStr"/>
+      <c r="K725" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L725" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44746,7 +46682,11 @@
           <t>77.020.146-2</t>
         </is>
       </c>
-      <c r="K726" t="inlineStr"/>
+      <c r="K726" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L726" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44868,7 +46808,11 @@
           <t>77.801.815-2</t>
         </is>
       </c>
-      <c r="K728" t="inlineStr"/>
+      <c r="K728" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L728" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44929,7 +46873,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K729" t="inlineStr"/>
+      <c r="K729" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L729" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44990,7 +46938,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K730" t="inlineStr"/>
+      <c r="K730" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L730" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45173,7 +47125,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K733" t="inlineStr"/>
+      <c r="K733" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L733" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45356,7 +47312,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K736" t="inlineStr"/>
+      <c r="K736" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L736" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45417,7 +47377,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K737" t="inlineStr"/>
+      <c r="K737" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L737" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45478,7 +47442,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K738" t="inlineStr"/>
+      <c r="K738" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L738" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45539,7 +47507,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K739" t="inlineStr"/>
+      <c r="K739" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L739" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45661,7 +47633,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K741" t="inlineStr"/>
+      <c r="K741" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L741" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45783,7 +47759,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K743" t="inlineStr"/>
+      <c r="K743" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L743" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45905,7 +47885,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K745" t="inlineStr"/>
+      <c r="K745" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L745" t="inlineStr">
         <is>
           <t>USD</t>
@@ -46088,7 +48072,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K748" t="inlineStr"/>
+      <c r="K748" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L748" t="inlineStr">
         <is>
           <t>USD</t>
@@ -46149,7 +48137,11 @@
           <t>78.212.867-1</t>
         </is>
       </c>
-      <c r="K749" t="inlineStr"/>
+      <c r="K749" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L749" t="inlineStr">
         <is>
           <t>USD</t>
@@ -46210,7 +48202,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K750" t="inlineStr"/>
+      <c r="K750" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L750" t="inlineStr">
         <is>
           <t>USD</t>
@@ -46454,7 +48450,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K754" t="inlineStr"/>
+      <c r="K754" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L754" t="inlineStr">
         <is>
           <t>USD</t>
@@ -46820,7 +48820,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K760" t="inlineStr"/>
+      <c r="K760" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L760" t="inlineStr">
         <is>
           <t>USD</t>
@@ -46881,7 +48885,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K761" t="inlineStr"/>
+      <c r="K761" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L761" t="inlineStr">
         <is>
           <t>USD</t>
@@ -47003,7 +49011,11 @@
           <t>78.203.286-0</t>
         </is>
       </c>
-      <c r="K763" t="inlineStr"/>
+      <c r="K763" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L763" t="inlineStr">
         <is>
           <t>USD</t>
@@ -47064,7 +49076,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K764" t="inlineStr"/>
+      <c r="K764" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L764" t="inlineStr">
         <is>
           <t>USD</t>
@@ -47186,7 +49202,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K766" t="inlineStr"/>
+      <c r="K766" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L766" t="inlineStr">
         <is>
           <t>USD</t>
@@ -47308,7 +49328,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K768" t="inlineStr"/>
+      <c r="K768" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L768" t="inlineStr">
         <is>
           <t>USD</t>
@@ -47369,7 +49393,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K769" t="inlineStr"/>
+      <c r="K769" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L769" t="inlineStr">
         <is>
           <t>USD</t>
@@ -47430,7 +49458,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K770" t="inlineStr"/>
+      <c r="K770" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L770" t="inlineStr">
         <is>
           <t>USD</t>
@@ -47491,7 +49523,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K771" t="inlineStr"/>
+      <c r="K771" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L771" t="inlineStr">
         <is>
           <t>USD</t>
@@ -47552,7 +49588,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K772" t="inlineStr"/>
+      <c r="K772" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L772" t="inlineStr">
         <is>
           <t>USD</t>
@@ -47613,7 +49653,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K773" t="inlineStr"/>
+      <c r="K773" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L773" t="inlineStr">
         <is>
           <t>USD</t>
@@ -47735,7 +49779,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K775" t="inlineStr"/>
+      <c r="K775" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L775" t="inlineStr">
         <is>
           <t>USD</t>
@@ -47796,7 +49844,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K776" t="inlineStr"/>
+      <c r="K776" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L776" t="inlineStr">
         <is>
           <t>USD</t>
@@ -48040,7 +50092,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K780" t="inlineStr"/>
+      <c r="K780" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L780" t="inlineStr">
         <is>
           <t>USD</t>
@@ -48101,7 +50157,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K781" t="inlineStr"/>
+      <c r="K781" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L781" t="inlineStr">
         <is>
           <t>USD</t>
@@ -48162,7 +50222,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K782" t="inlineStr"/>
+      <c r="K782" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L782" t="inlineStr">
         <is>
           <t>USD</t>
@@ -48223,7 +50287,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K783" t="inlineStr"/>
+      <c r="K783" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L783" t="inlineStr">
         <is>
           <t>USD</t>
@@ -48284,7 +50352,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K784" t="inlineStr"/>
+      <c r="K784" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L784" t="inlineStr">
         <is>
           <t>USD</t>
@@ -48345,7 +50417,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K785" t="inlineStr"/>
+      <c r="K785" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L785" t="inlineStr">
         <is>
           <t>USD</t>
@@ -48406,7 +50482,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K786" t="inlineStr"/>
+      <c r="K786" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L786" t="inlineStr">
         <is>
           <t>USD</t>
@@ -48467,7 +50547,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K787" t="inlineStr"/>
+      <c r="K787" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L787" t="inlineStr">
         <is>
           <t>USD</t>
@@ -48528,7 +50612,11 @@
           <t>78.212.867-1</t>
         </is>
       </c>
-      <c r="K788" t="inlineStr"/>
+      <c r="K788" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L788" t="inlineStr">
         <is>
           <t>USD</t>
@@ -48589,7 +50677,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K789" t="inlineStr"/>
+      <c r="K789" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L789" t="inlineStr">
         <is>
           <t>USD</t>
@@ -48711,7 +50803,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K791" t="inlineStr"/>
+      <c r="K791" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L791" t="inlineStr">
         <is>
           <t>USD</t>
@@ -48772,7 +50868,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K792" t="inlineStr"/>
+      <c r="K792" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L792" t="inlineStr">
         <is>
           <t>USD</t>
@@ -48955,7 +51055,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K795" t="inlineStr"/>
+      <c r="K795" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L795" t="inlineStr">
         <is>
           <t>USD</t>
@@ -49016,7 +51120,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K796" t="inlineStr"/>
+      <c r="K796" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L796" t="inlineStr">
         <is>
           <t>USD</t>
@@ -49138,7 +51246,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K798" t="inlineStr"/>
+      <c r="K798" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L798" t="inlineStr">
         <is>
           <t>USD</t>
@@ -49260,7 +51372,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K800" t="inlineStr"/>
+      <c r="K800" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L800" t="inlineStr">
         <is>
           <t>USD</t>
@@ -49321,7 +51437,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K801" t="inlineStr"/>
+      <c r="K801" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L801" t="inlineStr">
         <is>
           <t>USD</t>
@@ -49382,7 +51502,11 @@
           <t>78.212.867-1</t>
         </is>
       </c>
-      <c r="K802" t="inlineStr"/>
+      <c r="K802" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L802" t="inlineStr">
         <is>
           <t>USD</t>
@@ -49504,7 +51628,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K804" t="inlineStr"/>
+      <c r="K804" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L804" t="inlineStr">
         <is>
           <t>USD</t>
@@ -49626,7 +51754,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K806" t="inlineStr"/>
+      <c r="K806" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L806" t="inlineStr">
         <is>
           <t>USD</t>
@@ -49687,7 +51819,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K807" t="inlineStr"/>
+      <c r="K807" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L807" t="inlineStr">
         <is>
           <t>USD</t>
@@ -49748,7 +51884,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K808" t="inlineStr"/>
+      <c r="K808" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L808" t="inlineStr">
         <is>
           <t>USD</t>
@@ -49809,7 +51949,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K809" t="inlineStr"/>
+      <c r="K809" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L809" t="inlineStr">
         <is>
           <t>USD</t>
@@ -50114,7 +52258,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K814" t="inlineStr"/>
+      <c r="K814" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L814" t="inlineStr">
         <is>
           <t>USD</t>
@@ -50175,7 +52323,11 @@
           <t>78.209.441-6</t>
         </is>
       </c>
-      <c r="K815" t="inlineStr"/>
+      <c r="K815" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L815" t="inlineStr">
         <is>
           <t>USD</t>
@@ -50236,7 +52388,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K816" t="inlineStr"/>
+      <c r="K816" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L816" t="inlineStr">
         <is>
           <t>USD</t>
@@ -50358,7 +52514,11 @@
           <t>78.212.867-1</t>
         </is>
       </c>
-      <c r="K818" t="inlineStr"/>
+      <c r="K818" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L818" t="inlineStr">
         <is>
           <t>USD</t>
@@ -50419,7 +52579,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K819" t="inlineStr"/>
+      <c r="K819" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L819" t="inlineStr">
         <is>
           <t>USD</t>
@@ -50480,7 +52644,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K820" t="inlineStr"/>
+      <c r="K820" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L820" t="inlineStr">
         <is>
           <t>USD</t>
@@ -50541,7 +52709,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K821" t="inlineStr"/>
+      <c r="K821" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L821" t="inlineStr">
         <is>
           <t>USD</t>
@@ -50602,7 +52774,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K822" t="inlineStr"/>
+      <c r="K822" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L822" t="inlineStr">
         <is>
           <t>USD</t>
@@ -50724,7 +52900,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K824" t="inlineStr"/>
+      <c r="K824" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L824" t="inlineStr">
         <is>
           <t>USD</t>
@@ -50846,7 +53026,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K826" t="inlineStr"/>
+      <c r="K826" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L826" t="inlineStr">
         <is>
           <t>USD</t>
@@ -50907,7 +53091,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K827" t="inlineStr"/>
+      <c r="K827" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L827" t="inlineStr">
         <is>
           <t>USD</t>
@@ -50968,7 +53156,11 @@
           <t>78.307.990-9</t>
         </is>
       </c>
-      <c r="K828" t="inlineStr"/>
+      <c r="K828" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L828" t="inlineStr">
         <is>
           <t>USD</t>
@@ -51029,7 +53221,11 @@
           <t>77.649.678-2</t>
         </is>
       </c>
-      <c r="K829" t="inlineStr"/>
+      <c r="K829" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L829" t="inlineStr">
         <is>
           <t>USD</t>
@@ -51273,7 +53469,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K833" t="inlineStr"/>
+      <c r="K833" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L833" t="inlineStr">
         <is>
           <t>USD</t>
@@ -51395,7 +53595,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K835" t="inlineStr"/>
+      <c r="K835" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L835" t="inlineStr">
         <is>
           <t>USD</t>
@@ -51456,7 +53660,11 @@
           <t>76.102.347-0</t>
         </is>
       </c>
-      <c r="K836" t="inlineStr"/>
+      <c r="K836" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L836" t="inlineStr">
         <is>
           <t>USD</t>
@@ -51517,7 +53725,11 @@
           <t>76.556.184-1</t>
         </is>
       </c>
-      <c r="K837" t="inlineStr"/>
+      <c r="K837" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L837" t="inlineStr">
         <is>
           <t>USD</t>
@@ -51578,7 +53790,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K838" t="inlineStr"/>
+      <c r="K838" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L838" t="inlineStr">
         <is>
           <t>USD</t>
@@ -51639,7 +53855,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K839" t="inlineStr"/>
+      <c r="K839" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L839" t="inlineStr">
         <is>
           <t>USD</t>
@@ -51761,7 +53981,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K841" t="inlineStr"/>
+      <c r="K841" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L841" t="inlineStr">
         <is>
           <t>USD</t>
@@ -51883,7 +54107,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K843" t="inlineStr"/>
+      <c r="K843" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L843" t="inlineStr">
         <is>
           <t>USD</t>
@@ -51944,7 +54172,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K844" t="inlineStr"/>
+      <c r="K844" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L844" t="inlineStr">
         <is>
           <t>USD</t>
@@ -52005,7 +54237,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K845" t="inlineStr"/>
+      <c r="K845" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L845" t="inlineStr">
         <is>
           <t>USD</t>
@@ -52066,7 +54302,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K846" t="inlineStr"/>
+      <c r="K846" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L846" t="inlineStr">
         <is>
           <t>USD</t>
@@ -52127,7 +54367,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K847" t="inlineStr"/>
+      <c r="K847" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L847" t="inlineStr">
         <is>
           <t>USD</t>
@@ -52188,7 +54432,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K848" t="inlineStr"/>
+      <c r="K848" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L848" t="inlineStr">
         <is>
           <t>USD</t>
@@ -52249,7 +54497,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K849" t="inlineStr"/>
+      <c r="K849" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L849" t="inlineStr">
         <is>
           <t>USD</t>
@@ -52310,7 +54562,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K850" t="inlineStr"/>
+      <c r="K850" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L850" t="inlineStr">
         <is>
           <t>USD</t>
@@ -52371,7 +54627,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K851" t="inlineStr"/>
+      <c r="K851" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L851" t="inlineStr">
         <is>
           <t>USD</t>
@@ -52432,7 +54692,11 @@
           <t>78.212.867-1</t>
         </is>
       </c>
-      <c r="K852" t="inlineStr"/>
+      <c r="K852" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L852" t="inlineStr">
         <is>
           <t>USD</t>
@@ -52554,7 +54818,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K854" t="inlineStr"/>
+      <c r="K854" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L854" t="inlineStr">
         <is>
           <t>USD</t>
@@ -52615,7 +54883,11 @@
           <t>78.209.481-5</t>
         </is>
       </c>
-      <c r="K855" t="inlineStr"/>
+      <c r="K855" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L855" t="inlineStr">
         <is>
           <t>USD</t>
@@ -52676,7 +54948,11 @@
           <t>77.619.564-2</t>
         </is>
       </c>
-      <c r="K856" t="inlineStr"/>
+      <c r="K856" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L856" t="inlineStr">
         <is>
           <t>USD</t>
@@ -52737,7 +55013,11 @@
           <t>77.082.051-0</t>
         </is>
       </c>
-      <c r="K857" t="inlineStr"/>
+      <c r="K857" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L857" t="inlineStr">
         <is>
           <t>USD</t>
@@ -52859,7 +55139,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K859" t="inlineStr"/>
+      <c r="K859" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L859" t="inlineStr">
         <is>
           <t>USD</t>
@@ -52920,7 +55204,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K860" t="inlineStr"/>
+      <c r="K860" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L860" t="inlineStr">
         <is>
           <t>USD</t>
@@ -53042,7 +55330,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K862" t="inlineStr"/>
+      <c r="K862" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L862" t="inlineStr">
         <is>
           <t>USD</t>
@@ -53103,7 +55395,11 @@
           <t>79.722.860-5</t>
         </is>
       </c>
-      <c r="K863" t="inlineStr"/>
+      <c r="K863" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L863" t="inlineStr">
         <is>
           <t>USD</t>
@@ -53164,7 +55460,11 @@
           <t>78.061.716-0</t>
         </is>
       </c>
-      <c r="K864" t="inlineStr"/>
+      <c r="K864" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L864" t="inlineStr">
         <is>
           <t>USD</t>
@@ -53225,7 +55525,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K865" t="inlineStr"/>
+      <c r="K865" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L865" t="inlineStr">
         <is>
           <t>USD</t>
@@ -53286,7 +55590,11 @@
           <t>78.209.441-6</t>
         </is>
       </c>
-      <c r="K866" t="inlineStr"/>
+      <c r="K866" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L866" t="inlineStr">
         <is>
           <t>USD</t>
@@ -53408,7 +55716,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K868" t="inlineStr"/>
+      <c r="K868" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L868" t="inlineStr">
         <is>
           <t>USD</t>
@@ -53530,7 +55842,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K870" t="inlineStr"/>
+      <c r="K870" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L870" t="inlineStr">
         <is>
           <t>USD</t>
@@ -53591,7 +55907,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K871" t="inlineStr"/>
+      <c r="K871" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L871" t="inlineStr">
         <is>
           <t>USD</t>
@@ -53652,7 +55972,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K872" t="inlineStr"/>
+      <c r="K872" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L872" t="inlineStr">
         <is>
           <t>USD</t>
@@ -53713,7 +56037,11 @@
           <t>77.745.829-9</t>
         </is>
       </c>
-      <c r="K873" t="inlineStr"/>
+      <c r="K873" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L873" t="inlineStr">
         <is>
           <t>USD</t>
@@ -53774,7 +56102,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K874" t="inlineStr"/>
+      <c r="K874" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L874" t="inlineStr">
         <is>
           <t>USD</t>
@@ -53835,7 +56167,11 @@
           <t>77.406.941-0</t>
         </is>
       </c>
-      <c r="K875" t="inlineStr"/>
+      <c r="K875" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L875" t="inlineStr">
         <is>
           <t>USD</t>
@@ -53957,7 +56293,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K877" t="inlineStr"/>
+      <c r="K877" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L877" t="inlineStr">
         <is>
           <t>USD</t>
@@ -54018,7 +56358,11 @@
           <t>76.525.922-3</t>
         </is>
       </c>
-      <c r="K878" t="inlineStr"/>
+      <c r="K878" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L878" t="inlineStr">
         <is>
           <t>USD</t>
@@ -54079,7 +56423,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K879" t="inlineStr"/>
+      <c r="K879" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L879" t="inlineStr">
         <is>
           <t>USD</t>
@@ -54140,7 +56488,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K880" t="inlineStr"/>
+      <c r="K880" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L880" t="inlineStr">
         <is>
           <t>USD</t>
@@ -54262,7 +56614,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K882" t="inlineStr"/>
+      <c r="K882" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L882" t="inlineStr">
         <is>
           <t>USD</t>
@@ -54323,7 +56679,11 @@
           <t>78.212.867-1</t>
         </is>
       </c>
-      <c r="K883" t="inlineStr"/>
+      <c r="K883" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L883" t="inlineStr">
         <is>
           <t>USD</t>
@@ -54384,7 +56744,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K884" t="inlineStr"/>
+      <c r="K884" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L884" t="inlineStr">
         <is>
           <t>USD</t>
@@ -54506,7 +56870,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K886" t="inlineStr"/>
+      <c r="K886" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L886" t="inlineStr">
         <is>
           <t>USD</t>
@@ -54689,7 +57057,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K889" t="inlineStr"/>
+      <c r="K889" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L889" t="inlineStr">
         <is>
           <t>USD</t>
@@ -54811,7 +57183,11 @@
           <t>76.539.061-3</t>
         </is>
       </c>
-      <c r="K891" t="inlineStr"/>
+      <c r="K891" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L891" t="inlineStr">
         <is>
           <t>USD</t>
@@ -54872,7 +57248,11 @@
           <t>76.100.933-8</t>
         </is>
       </c>
-      <c r="K892" t="inlineStr"/>
+      <c r="K892" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L892" t="inlineStr">
         <is>
           <t>USD</t>
@@ -54933,7 +57313,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K893" t="inlineStr"/>
+      <c r="K893" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L893" t="inlineStr">
         <is>
           <t>USD</t>
@@ -55055,7 +57439,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K895" t="inlineStr"/>
+      <c r="K895" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L895" t="inlineStr">
         <is>
           <t>USD</t>
@@ -55177,7 +57565,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K897" t="inlineStr"/>
+      <c r="K897" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L897" t="inlineStr">
         <is>
           <t>USD</t>
@@ -55360,7 +57752,11 @@
           <t>77.619.564-2</t>
         </is>
       </c>
-      <c r="K900" t="inlineStr"/>
+      <c r="K900" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L900" t="inlineStr">
         <is>
           <t>USD</t>
@@ -55482,7 +57878,11 @@
           <t>78.209.499-8</t>
         </is>
       </c>
-      <c r="K902" t="inlineStr"/>
+      <c r="K902" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L902" t="inlineStr">
         <is>
           <t>USD</t>
@@ -55543,7 +57943,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K903" t="inlineStr"/>
+      <c r="K903" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L903" t="inlineStr">
         <is>
           <t>USD</t>
@@ -55665,7 +58069,11 @@
           <t>19.260.495-8</t>
         </is>
       </c>
-      <c r="K905" t="inlineStr"/>
+      <c r="K905" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L905" t="inlineStr">
         <is>
           <t>USD</t>
@@ -55726,7 +58134,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K906" t="inlineStr"/>
+      <c r="K906" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L906" t="inlineStr">
         <is>
           <t>USD</t>
@@ -55787,7 +58199,11 @@
           <t>78.076.237-3</t>
         </is>
       </c>
-      <c r="K907" t="inlineStr"/>
+      <c r="K907" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L907" t="inlineStr">
         <is>
           <t>USD</t>
@@ -55909,7 +58325,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K909" t="inlineStr"/>
+      <c r="K909" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L909" t="inlineStr">
         <is>
           <t>USD</t>
@@ -55970,7 +58390,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K910" t="inlineStr"/>
+      <c r="K910" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L910" t="inlineStr">
         <is>
           <t>USD</t>
@@ -56214,7 +58638,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K914" t="inlineStr"/>
+      <c r="K914" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L914" t="inlineStr">
         <is>
           <t>USD</t>
@@ -56275,7 +58703,11 @@
           <t>77.404.653-4</t>
         </is>
       </c>
-      <c r="K915" t="inlineStr"/>
+      <c r="K915" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L915" t="inlineStr">
         <is>
           <t>USD</t>
@@ -56397,7 +58829,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K917" t="inlineStr"/>
+      <c r="K917" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L917" t="inlineStr">
         <is>
           <t>USD</t>
@@ -56458,7 +58894,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K918" t="inlineStr"/>
+      <c r="K918" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L918" t="inlineStr">
         <is>
           <t>USD</t>
@@ -56641,7 +59081,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K921" t="inlineStr"/>
+      <c r="K921" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L921" t="inlineStr">
         <is>
           <t>USD</t>
@@ -56885,7 +59329,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K925" t="inlineStr"/>
+      <c r="K925" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L925" t="inlineStr">
         <is>
           <t>USD</t>
@@ -57312,7 +59760,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K932" t="inlineStr"/>
+      <c r="K932" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L932" t="inlineStr">
         <is>
           <t>USD</t>
@@ -57495,7 +59947,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K935" t="inlineStr"/>
+      <c r="K935" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L935" t="inlineStr">
         <is>
           <t>USD</t>
@@ -57556,7 +60012,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K936" t="inlineStr"/>
+      <c r="K936" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L936" t="inlineStr">
         <is>
           <t>USD</t>
@@ -57739,7 +60199,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K939" t="inlineStr"/>
+      <c r="K939" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L939" t="inlineStr">
         <is>
           <t>USD</t>
@@ -57800,7 +60264,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K940" t="inlineStr"/>
+      <c r="K940" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L940" t="inlineStr">
         <is>
           <t>USD</t>
@@ -57861,7 +60329,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K941" t="inlineStr"/>
+      <c r="K941" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L941" t="inlineStr">
         <is>
           <t>USD</t>
@@ -57983,7 +60455,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K943" t="inlineStr"/>
+      <c r="K943" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L943" t="inlineStr">
         <is>
           <t>USD</t>
@@ -58044,7 +60520,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K944" t="inlineStr"/>
+      <c r="K944" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L944" t="inlineStr">
         <is>
           <t>USD</t>
@@ -58105,7 +60585,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K945" t="inlineStr"/>
+      <c r="K945" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L945" t="inlineStr">
         <is>
           <t>USD</t>
@@ -58166,7 +60650,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K946" t="inlineStr"/>
+      <c r="K946" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L946" t="inlineStr">
         <is>
           <t>USD</t>
@@ -58227,7 +60715,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K947" t="inlineStr"/>
+      <c r="K947" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L947" t="inlineStr">
         <is>
           <t>USD</t>
@@ -58288,7 +60780,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K948" t="inlineStr"/>
+      <c r="K948" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L948" t="inlineStr">
         <is>
           <t>USD</t>
@@ -58410,7 +60906,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K950" t="inlineStr"/>
+      <c r="K950" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L950" t="inlineStr">
         <is>
           <t>USD</t>
@@ -58471,7 +60971,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K951" t="inlineStr"/>
+      <c r="K951" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L951" t="inlineStr">
         <is>
           <t>USD</t>
@@ -58532,7 +61036,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K952" t="inlineStr"/>
+      <c r="K952" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L952" t="inlineStr">
         <is>
           <t>USD</t>
@@ -58593,7 +61101,11 @@
           <t>77.623.039-1</t>
         </is>
       </c>
-      <c r="K953" t="inlineStr"/>
+      <c r="K953" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L953" t="inlineStr">
         <is>
           <t>USD</t>
@@ -58654,7 +61166,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K954" t="inlineStr"/>
+      <c r="K954" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L954" t="inlineStr">
         <is>
           <t>USD</t>
@@ -58776,7 +61292,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K956" t="inlineStr"/>
+      <c r="K956" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L956" t="inlineStr">
         <is>
           <t>USD</t>
@@ -59020,7 +61540,11 @@
           <t>77.806.000-0</t>
         </is>
       </c>
-      <c r="K960" t="inlineStr"/>
+      <c r="K960" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L960" t="inlineStr">
         <is>
           <t>USD</t>
@@ -59264,7 +61788,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K964" t="inlineStr"/>
+      <c r="K964" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L964" t="inlineStr">
         <is>
           <t>USD</t>
@@ -59325,7 +61853,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K965" t="inlineStr"/>
+      <c r="K965" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L965" t="inlineStr">
         <is>
           <t>USD</t>
@@ -59447,7 +61979,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K967" t="inlineStr"/>
+      <c r="K967" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L967" t="inlineStr">
         <is>
           <t>USD</t>
@@ -59569,7 +62105,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K969" t="inlineStr"/>
+      <c r="K969" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L969" t="inlineStr">
         <is>
           <t>USD</t>
@@ -59630,7 +62170,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K970" t="inlineStr"/>
+      <c r="K970" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L970" t="inlineStr">
         <is>
           <t>USD</t>
@@ -59813,7 +62357,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K973" t="inlineStr"/>
+      <c r="K973" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L973" t="inlineStr">
         <is>
           <t>USD</t>
@@ -59874,7 +62422,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K974" t="inlineStr"/>
+      <c r="K974" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L974" t="inlineStr">
         <is>
           <t>USD</t>
@@ -59935,7 +62487,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K975" t="inlineStr"/>
+      <c r="K975" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L975" t="inlineStr">
         <is>
           <t>USD</t>
@@ -59996,7 +62552,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K976" t="inlineStr"/>
+      <c r="K976" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L976" t="inlineStr">
         <is>
           <t>USD</t>
@@ -60057,7 +62617,11 @@
           <t>78.307.990-9</t>
         </is>
       </c>
-      <c r="K977" t="inlineStr"/>
+      <c r="K977" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L977" t="inlineStr">
         <is>
           <t>USD</t>
@@ -60118,7 +62682,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K978" t="inlineStr"/>
+      <c r="K978" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L978" t="inlineStr">
         <is>
           <t>USD</t>
@@ -60179,7 +62747,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K979" t="inlineStr"/>
+      <c r="K979" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L979" t="inlineStr">
         <is>
           <t>USD</t>
@@ -60240,7 +62812,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K980" t="inlineStr"/>
+      <c r="K980" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L980" t="inlineStr">
         <is>
           <t>USD</t>
@@ -60362,7 +62938,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K982" t="inlineStr"/>
+      <c r="K982" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L982" t="inlineStr">
         <is>
           <t>USD</t>
@@ -60423,7 +63003,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K983" t="inlineStr"/>
+      <c r="K983" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L983" t="inlineStr">
         <is>
           <t>USD</t>
@@ -60484,7 +63068,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K984" t="inlineStr"/>
+      <c r="K984" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L984" t="inlineStr">
         <is>
           <t>USD</t>
@@ -60545,7 +63133,11 @@
           <t>78.212.867-1</t>
         </is>
       </c>
-      <c r="K985" t="inlineStr"/>
+      <c r="K985" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L985" t="inlineStr">
         <is>
           <t>USD</t>
@@ -60667,7 +63259,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K987" t="inlineStr"/>
+      <c r="K987" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L987" t="inlineStr">
         <is>
           <t>USD</t>
@@ -60789,7 +63385,11 @@
           <t>77.806.000-0</t>
         </is>
       </c>
-      <c r="K989" t="inlineStr"/>
+      <c r="K989" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L989" t="inlineStr">
         <is>
           <t>USD</t>
@@ -60850,7 +63450,11 @@
           <t>78.212.867-1</t>
         </is>
       </c>
-      <c r="K990" t="inlineStr"/>
+      <c r="K990" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L990" t="inlineStr">
         <is>
           <t>USD</t>
@@ -60911,7 +63515,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K991" t="inlineStr"/>
+      <c r="K991" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L991" t="inlineStr">
         <is>
           <t>USD</t>
@@ -61033,7 +63641,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K993" t="inlineStr"/>
+      <c r="K993" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L993" t="inlineStr">
         <is>
           <t>USD</t>
@@ -61094,7 +63706,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K994" t="inlineStr"/>
+      <c r="K994" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L994" t="inlineStr">
         <is>
           <t>USD</t>
@@ -61460,7 +64076,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K1000" t="inlineStr"/>
+      <c r="K1000" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L1000" t="inlineStr">
         <is>
           <t>USD</t>
@@ -61521,7 +64141,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K1001" t="inlineStr"/>
+      <c r="K1001" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L1001" t="inlineStr">
         <is>
           <t>USD</t>
@@ -61643,7 +64267,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K1003" t="inlineStr"/>
+      <c r="K1003" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L1003" t="inlineStr">
         <is>
           <t>USD</t>
@@ -61887,7 +64515,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K1007" t="inlineStr"/>
+      <c r="K1007" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L1007" t="inlineStr">
         <is>
           <t>USD</t>
@@ -61948,7 +64580,11 @@
           <t>77.909.208-9</t>
         </is>
       </c>
-      <c r="K1008" t="inlineStr"/>
+      <c r="K1008" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L1008" t="inlineStr">
         <is>
           <t>USD</t>
@@ -62070,7 +64706,11 @@
           <t>78.212.867-1</t>
         </is>
       </c>
-      <c r="K1010" t="inlineStr"/>
+      <c r="K1010" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L1010" t="inlineStr">
         <is>
           <t>USD</t>
@@ -62131,7 +64771,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K1011" t="inlineStr"/>
+      <c r="K1011" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L1011" t="inlineStr">
         <is>
           <t>USD</t>
@@ -62253,7 +64897,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K1013" t="inlineStr"/>
+      <c r="K1013" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L1013" t="inlineStr">
         <is>
           <t>USD</t>
@@ -62314,7 +64962,11 @@
           <t>76.556.184-1</t>
         </is>
       </c>
-      <c r="K1014" t="inlineStr"/>
+      <c r="K1014" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L1014" t="inlineStr">
         <is>
           <t>USD</t>
@@ -62375,7 +65027,11 @@
           <t>78.199.695-5</t>
         </is>
       </c>
-      <c r="K1015" t="inlineStr"/>
+      <c r="K1015" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L1015" t="inlineStr">
         <is>
           <t>USD</t>
@@ -62558,7 +65214,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K1018" t="inlineStr"/>
+      <c r="K1018" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L1018" t="inlineStr">
         <is>
           <t>USD</t>
@@ -62680,7 +65340,11 @@
           <t>78.307.990-9</t>
         </is>
       </c>
-      <c r="K1020" t="inlineStr"/>
+      <c r="K1020" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L1020" t="inlineStr">
         <is>
           <t>USD</t>
@@ -62741,7 +65405,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K1021" t="inlineStr"/>
+      <c r="K1021" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L1021" t="inlineStr">
         <is>
           <t>USD</t>
@@ -62802,7 +65470,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K1022" t="inlineStr"/>
+      <c r="K1022" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L1022" t="inlineStr">
         <is>
           <t>USD</t>
@@ -62863,7 +65535,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K1023" t="inlineStr"/>
+      <c r="K1023" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L1023" t="inlineStr">
         <is>
           <t>USD</t>
@@ -62924,7 +65600,11 @@
           <t>78.307.990-9</t>
         </is>
       </c>
-      <c r="K1024" t="inlineStr"/>
+      <c r="K1024" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L1024" t="inlineStr">
         <is>
           <t>USD</t>
@@ -63046,7 +65726,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K1026" t="inlineStr"/>
+      <c r="K1026" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L1026" t="inlineStr">
         <is>
           <t>USD</t>
@@ -63107,7 +65791,11 @@
           <t>77.581.865-4</t>
         </is>
       </c>
-      <c r="K1027" t="inlineStr"/>
+      <c r="K1027" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L1027" t="inlineStr">
         <is>
           <t>USD</t>
@@ -63168,7 +65856,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K1028" t="inlineStr"/>
+      <c r="K1028" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L1028" t="inlineStr">
         <is>
           <t>USD</t>
@@ -63229,7 +65921,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K1029" t="inlineStr"/>
+      <c r="K1029" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L1029" t="inlineStr">
         <is>
           <t>USD</t>
@@ -63290,7 +65986,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K1030" t="inlineStr"/>
+      <c r="K1030" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L1030" t="inlineStr">
         <is>
           <t>USD</t>
@@ -63412,7 +66112,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K1032" t="inlineStr"/>
+      <c r="K1032" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L1032" t="inlineStr">
         <is>
           <t>USD</t>
@@ -63534,7 +66238,11 @@
           <t>78.307.990-9</t>
         </is>
       </c>
-      <c r="K1034" t="inlineStr"/>
+      <c r="K1034" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L1034" t="inlineStr">
         <is>
           <t>USD</t>
@@ -63595,7 +66303,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K1035" t="inlineStr"/>
+      <c r="K1035" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L1035" t="inlineStr">
         <is>
           <t>USD</t>
@@ -63656,7 +66368,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K1036" t="inlineStr"/>
+      <c r="K1036" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L1036" t="inlineStr">
         <is>
           <t>USD</t>
@@ -63717,7 +66433,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K1037" t="inlineStr"/>
+      <c r="K1037" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L1037" t="inlineStr">
         <is>
           <t>USD</t>
@@ -63778,7 +66498,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K1038" t="inlineStr"/>
+      <c r="K1038" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L1038" t="inlineStr">
         <is>
           <t>USD</t>
@@ -63839,7 +66563,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K1039" t="inlineStr"/>
+      <c r="K1039" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L1039" t="inlineStr">
         <is>
           <t>USD</t>
@@ -63961,7 +66689,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K1041" t="inlineStr"/>
+      <c r="K1041" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L1041" t="inlineStr">
         <is>
           <t>USD</t>
@@ -64022,7 +66754,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K1042" t="inlineStr"/>
+      <c r="K1042" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L1042" t="inlineStr">
         <is>
           <t>USD</t>
@@ -64144,7 +66880,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K1044" t="inlineStr"/>
+      <c r="K1044" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L1044" t="inlineStr">
         <is>
           <t>USD</t>
@@ -64205,7 +66945,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K1045" t="inlineStr"/>
+      <c r="K1045" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L1045" t="inlineStr">
         <is>
           <t>USD</t>
@@ -64327,7 +67071,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K1047" t="inlineStr"/>
+      <c r="K1047" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L1047" t="inlineStr">
         <is>
           <t>USD</t>
@@ -64388,7 +67136,11 @@
           <t>77.806.000-0</t>
         </is>
       </c>
-      <c r="K1048" t="inlineStr"/>
+      <c r="K1048" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L1048" t="inlineStr">
         <is>
           <t>USD</t>
@@ -64510,7 +67262,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K1050" t="inlineStr"/>
+      <c r="K1050" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L1050" t="inlineStr">
         <is>
           <t>USD</t>
@@ -64632,7 +67388,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K1052" t="inlineStr"/>
+      <c r="K1052" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L1052" t="inlineStr">
         <is>
           <t>USD</t>
@@ -64754,7 +67514,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K1054" t="inlineStr"/>
+      <c r="K1054" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L1054" t="inlineStr">
         <is>
           <t>USD</t>
@@ -64815,7 +67579,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K1055" t="inlineStr"/>
+      <c r="K1055" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L1055" t="inlineStr">
         <is>
           <t>USD</t>
@@ -64876,7 +67644,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K1056" t="inlineStr"/>
+      <c r="K1056" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L1056" t="inlineStr">
         <is>
           <t>USD</t>
@@ -65059,7 +67831,11 @@
           <t>78.188.383-2</t>
         </is>
       </c>
-      <c r="K1059" t="inlineStr"/>
+      <c r="K1059" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L1059" t="inlineStr">
         <is>
           <t>USD</t>
@@ -65120,7 +67896,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K1060" t="inlineStr"/>
+      <c r="K1060" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L1060" t="inlineStr">
         <is>
           <t>USD</t>
@@ -65181,7 +67961,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K1061" t="inlineStr"/>
+      <c r="K1061" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L1061" t="inlineStr">
         <is>
           <t>USD</t>
@@ -65303,7 +68087,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K1063" t="inlineStr"/>
+      <c r="K1063" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L1063" t="inlineStr">
         <is>
           <t>USD</t>
@@ -65364,7 +68152,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K1064" t="inlineStr"/>
+      <c r="K1064" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L1064" t="inlineStr">
         <is>
           <t>USD</t>
@@ -65425,7 +68217,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K1065" t="inlineStr"/>
+      <c r="K1065" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L1065" t="inlineStr">
         <is>
           <t>USD</t>
@@ -65486,7 +68282,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K1066" t="inlineStr"/>
+      <c r="K1066" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L1066" t="inlineStr">
         <is>
           <t>USD</t>
@@ -65669,7 +68469,11 @@
           <t>77.610.393-4</t>
         </is>
       </c>
-      <c r="K1069" t="inlineStr"/>
+      <c r="K1069" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L1069" t="inlineStr">
         <is>
           <t>USD</t>
@@ -65791,7 +68595,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K1071" t="inlineStr"/>
+      <c r="K1071" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L1071" t="inlineStr">
         <is>
           <t>USD</t>
@@ -65913,7 +68721,11 @@
           <t>78.209.499-8</t>
         </is>
       </c>
-      <c r="K1073" t="inlineStr"/>
+      <c r="K1073" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L1073" t="inlineStr">
         <is>
           <t>USD</t>
@@ -65974,7 +68786,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K1074" t="inlineStr"/>
+      <c r="K1074" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L1074" t="inlineStr">
         <is>
           <t>USD</t>
@@ -66157,7 +68973,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K1077" t="inlineStr"/>
+      <c r="K1077" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L1077" t="inlineStr">
         <is>
           <t>USD</t>
@@ -66279,7 +69099,11 @@
           <t>78.209.441-6</t>
         </is>
       </c>
-      <c r="K1079" t="inlineStr"/>
+      <c r="K1079" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L1079" t="inlineStr">
         <is>
           <t>USD</t>
@@ -66340,7 +69164,11 @@
           <t>78.212.867-1</t>
         </is>
       </c>
-      <c r="K1080" t="inlineStr"/>
+      <c r="K1080" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L1080" t="inlineStr">
         <is>
           <t>USD</t>
@@ -66462,7 +69290,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K1082" t="inlineStr"/>
+      <c r="K1082" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L1082" t="inlineStr">
         <is>
           <t>USD</t>
@@ -66523,7 +69355,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K1083" t="inlineStr"/>
+      <c r="K1083" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L1083" t="inlineStr">
         <is>
           <t>USD</t>
@@ -66584,7 +69420,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K1084" t="inlineStr"/>
+      <c r="K1084" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L1084" t="inlineStr">
         <is>
           <t>USD</t>
@@ -66645,7 +69485,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K1085" t="inlineStr"/>
+      <c r="K1085" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L1085" t="inlineStr">
         <is>
           <t>USD</t>
@@ -66767,7 +69611,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K1087" t="inlineStr"/>
+      <c r="K1087" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L1087" t="inlineStr">
         <is>
           <t>USD</t>
@@ -66889,7 +69737,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K1089" t="inlineStr"/>
+      <c r="K1089" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L1089" t="inlineStr">
         <is>
           <t>USD</t>
@@ -67072,7 +69924,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K1092" t="inlineStr"/>
+      <c r="K1092" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L1092" t="inlineStr">
         <is>
           <t>USD</t>
@@ -67259,7 +70115,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K1095" t="inlineStr"/>
+      <c r="K1095" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L1095" t="inlineStr">
         <is>
           <t>USD</t>
@@ -67320,7 +70180,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K1096" t="inlineStr"/>
+      <c r="K1096" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L1096" t="inlineStr">
         <is>
           <t>USD</t>
@@ -67381,7 +70245,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K1097" t="inlineStr"/>
+      <c r="K1097" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L1097" t="inlineStr">
         <is>
           <t>USD</t>
@@ -67442,7 +70310,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K1098" t="inlineStr"/>
+      <c r="K1098" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L1098" t="inlineStr">
         <is>
           <t>USD</t>
@@ -67564,7 +70436,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K1100" t="inlineStr"/>
+      <c r="K1100" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L1100" t="inlineStr">
         <is>
           <t>USD</t>
@@ -67625,7 +70501,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K1101" t="inlineStr"/>
+      <c r="K1101" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L1101" t="inlineStr">
         <is>
           <t>USD</t>
@@ -67686,7 +70566,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K1102" t="inlineStr"/>
+      <c r="K1102" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L1102" t="inlineStr">
         <is>
           <t>USD</t>
@@ -67747,7 +70631,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K1103" t="inlineStr"/>
+      <c r="K1103" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L1103" t="inlineStr">
         <is>
           <t>USD</t>
@@ -67869,7 +70757,11 @@
           <t>19.260.495-8</t>
         </is>
       </c>
-      <c r="K1105" t="inlineStr"/>
+      <c r="K1105" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L1105" t="inlineStr">
         <is>
           <t>USD</t>
@@ -67930,7 +70822,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K1106" t="inlineStr"/>
+      <c r="K1106" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L1106" t="inlineStr">
         <is>
           <t>USD</t>
@@ -67991,7 +70887,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K1107" t="inlineStr"/>
+      <c r="K1107" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L1107" t="inlineStr">
         <is>
           <t>USD</t>
@@ -68052,7 +70952,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K1108" t="inlineStr"/>
+      <c r="K1108" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L1108" t="inlineStr">
         <is>
           <t>USD</t>
@@ -68113,7 +71017,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K1109" t="inlineStr"/>
+      <c r="K1109" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L1109" t="inlineStr">
         <is>
           <t>USD</t>
@@ -68174,7 +71082,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K1110" t="inlineStr"/>
+      <c r="K1110" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L1110" t="inlineStr">
         <is>
           <t>USD</t>
@@ -68235,7 +71147,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K1111" t="inlineStr"/>
+      <c r="K1111" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L1111" t="inlineStr">
         <is>
           <t>USD</t>
@@ -68296,7 +71212,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K1112" t="inlineStr"/>
+      <c r="K1112" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L1112" t="inlineStr">
         <is>
           <t>USD</t>
@@ -68479,7 +71399,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K1115" t="inlineStr"/>
+      <c r="K1115" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L1115" t="inlineStr">
         <is>
           <t>USD</t>
@@ -68601,7 +71525,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K1117" t="inlineStr"/>
+      <c r="K1117" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L1117" t="inlineStr">
         <is>
           <t>USD</t>

--- a/docs/oc-mensuales/articulos-de-aseo-e-higiene/abr-2026.xlsx
+++ b/docs/oc-mensuales/articulos-de-aseo-e-higiene/abr-2026.xlsx
@@ -1338,7 +1338,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1594,7 +1598,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1915,7 +1923,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L23" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3520,7 +3532,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr"/>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L48" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3772,7 +3788,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr"/>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L52" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4093,7 +4113,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr"/>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L57" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4284,7 +4308,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K60" t="inlineStr"/>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L60" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4345,7 +4373,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr"/>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L61" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4532,7 +4564,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K64" t="inlineStr"/>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L64" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5109,7 +5145,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K73" t="inlineStr"/>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L73" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5800,7 +5840,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K84" t="inlineStr"/>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L84" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6369,7 +6413,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K93" t="inlineStr"/>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L93" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6690,7 +6738,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K98" t="inlineStr"/>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L98" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7194,7 +7246,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K106" t="inlineStr"/>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L106" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7576,7 +7632,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K112" t="inlineStr"/>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L112" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8661,7 +8721,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K129" t="inlineStr"/>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L129" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9238,7 +9302,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K138" t="inlineStr"/>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L138" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9551,7 +9619,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K143" t="inlineStr"/>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L143" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9742,7 +9814,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K146" t="inlineStr"/>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L146" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10563,7 +10639,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K159" t="inlineStr"/>
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L159" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10689,7 +10769,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K161" t="inlineStr"/>
+      <c r="K161" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L161" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10815,7 +10899,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K163" t="inlineStr"/>
+      <c r="K163" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L163" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11518,7 +11606,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K174" t="inlineStr"/>
+      <c r="K174" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L174" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12221,7 +12313,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K185" t="inlineStr"/>
+      <c r="K185" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L185" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12343,7 +12439,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K187" t="inlineStr"/>
+      <c r="K187" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L187" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13688,7 +13788,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K208" t="inlineStr"/>
+      <c r="K208" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L208" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14456,7 +14560,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K220" t="inlineStr"/>
+      <c r="K220" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L220" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18438,7 +18546,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K282" t="inlineStr"/>
+      <c r="K282" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L282" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18499,7 +18611,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K283" t="inlineStr"/>
+      <c r="K283" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L283" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19271,7 +19387,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K295" t="inlineStr"/>
+      <c r="K295" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L295" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19393,7 +19513,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K297" t="inlineStr"/>
+      <c r="K297" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L297" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19645,7 +19769,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K301" t="inlineStr"/>
+      <c r="K301" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L301" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19706,7 +19834,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K302" t="inlineStr"/>
+      <c r="K302" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L302" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19767,7 +19899,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K303" t="inlineStr"/>
+      <c r="K303" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L303" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19828,7 +19964,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K304" t="inlineStr"/>
+      <c r="K304" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L304" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20210,7 +20350,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K310" t="inlineStr"/>
+      <c r="K310" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L310" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21490,7 +21634,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K330" t="inlineStr"/>
+      <c r="K330" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L330" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21872,7 +22020,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K336" t="inlineStr"/>
+      <c r="K336" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L336" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21998,7 +22150,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K338" t="inlineStr"/>
+      <c r="K338" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L338" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22124,7 +22280,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K340" t="inlineStr"/>
+      <c r="K340" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L340" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22311,7 +22471,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K343" t="inlineStr"/>
+      <c r="K343" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L343" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23368,7 +23532,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K360" t="inlineStr"/>
+      <c r="K360" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L360" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24197,7 +24365,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K373" t="inlineStr"/>
+      <c r="K373" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L373" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24896,7 +25068,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K384" t="inlineStr"/>
+      <c r="K384" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L384" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25022,7 +25198,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K386" t="inlineStr"/>
+      <c r="K386" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L386" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25148,7 +25328,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K388" t="inlineStr"/>
+      <c r="K388" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L388" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25339,7 +25523,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K391" t="inlineStr"/>
+      <c r="K391" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L391" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25465,7 +25653,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K393" t="inlineStr"/>
+      <c r="K393" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L393" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25786,7 +25978,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K398" t="inlineStr"/>
+      <c r="K398" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L398" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26038,7 +26234,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K402" t="inlineStr"/>
+      <c r="K402" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L402" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26741,7 +26941,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K413" t="inlineStr"/>
+      <c r="K413" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L413" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26867,7 +27071,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K415" t="inlineStr"/>
+      <c r="K415" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L415" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27188,7 +27396,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K420" t="inlineStr"/>
+      <c r="K420" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L420" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27314,7 +27526,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K422" t="inlineStr"/>
+      <c r="K422" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L422" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28533,7 +28749,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K441" t="inlineStr"/>
+      <c r="K441" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L441" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29496,7 +29716,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K456" t="inlineStr"/>
+      <c r="K456" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L456" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29557,7 +29781,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K457" t="inlineStr"/>
+      <c r="K457" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L457" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29744,7 +29972,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K460" t="inlineStr"/>
+      <c r="K460" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L460" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30451,7 +30683,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K471" t="inlineStr"/>
+      <c r="K471" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L471" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30768,7 +31004,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K476" t="inlineStr"/>
+      <c r="K476" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L476" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31597,7 +31837,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K489" t="inlineStr"/>
+      <c r="K489" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L489" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32930,7 +33174,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K510" t="inlineStr"/>
+      <c r="K510" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L510" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33564,7 +33812,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K520" t="inlineStr"/>
+      <c r="K520" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L520" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33881,7 +34133,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K525" t="inlineStr"/>
+      <c r="K525" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L525" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34446,7 +34702,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K534" t="inlineStr"/>
+      <c r="K534" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L534" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35974,7 +36234,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K558" t="inlineStr"/>
+      <c r="K558" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L558" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36100,7 +36364,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K560" t="inlineStr"/>
+      <c r="K560" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L560" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36356,7 +36624,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K564" t="inlineStr"/>
+      <c r="K564" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L564" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37567,7 +37839,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K583" t="inlineStr"/>
+      <c r="K583" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L583" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37758,7 +38034,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K586" t="inlineStr"/>
+      <c r="K586" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L586" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39428,7 +39708,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K612" t="inlineStr"/>
+      <c r="K612" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L612" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39550,7 +39834,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K614" t="inlineStr"/>
+      <c r="K614" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L614" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40062,7 +40350,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K622" t="inlineStr"/>
+      <c r="K622" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L622" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40761,7 +41053,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K633" t="inlineStr"/>
+      <c r="K633" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L633" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41517,7 +41813,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K645" t="inlineStr"/>
+      <c r="K645" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L645" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42606,7 +42906,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K662" t="inlineStr"/>
+      <c r="K662" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L662" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42988,7 +43292,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K668" t="inlineStr"/>
+      <c r="K668" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L668" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44203,7 +44511,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K687" t="inlineStr"/>
+      <c r="K687" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L687" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44390,7 +44702,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K690" t="inlineStr"/>
+      <c r="K690" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L690" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45032,7 +45348,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K700" t="inlineStr"/>
+      <c r="K700" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L700" t="inlineStr">
         <is>
           <t>USD</t>
@@ -47003,7 +47323,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K731" t="inlineStr"/>
+      <c r="K731" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L731" t="inlineStr">
         <is>
           <t>USD</t>
@@ -47064,7 +47388,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K732" t="inlineStr"/>
+      <c r="K732" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L732" t="inlineStr">
         <is>
           <t>USD</t>
@@ -47190,7 +47518,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K734" t="inlineStr"/>
+      <c r="K734" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L734" t="inlineStr">
         <is>
           <t>USD</t>
@@ -47251,7 +47583,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K735" t="inlineStr"/>
+      <c r="K735" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L735" t="inlineStr">
         <is>
           <t>USD</t>
@@ -47698,7 +48034,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K742" t="inlineStr"/>
+      <c r="K742" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L742" t="inlineStr">
         <is>
           <t>USD</t>
@@ -47824,7 +48164,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K744" t="inlineStr"/>
+      <c r="K744" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L744" t="inlineStr">
         <is>
           <t>USD</t>
@@ -48328,7 +48672,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K752" t="inlineStr"/>
+      <c r="K752" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L752" t="inlineStr">
         <is>
           <t>USD</t>
@@ -48576,7 +48924,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K756" t="inlineStr"/>
+      <c r="K756" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L756" t="inlineStr">
         <is>
           <t>USD</t>
@@ -48637,7 +48989,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K757" t="inlineStr"/>
+      <c r="K757" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L757" t="inlineStr">
         <is>
           <t>USD</t>
@@ -48759,7 +49115,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K759" t="inlineStr"/>
+      <c r="K759" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L759" t="inlineStr">
         <is>
           <t>USD</t>
@@ -49141,7 +49501,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K765" t="inlineStr"/>
+      <c r="K765" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L765" t="inlineStr">
         <is>
           <t>USD</t>
@@ -50742,7 +51106,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K790" t="inlineStr"/>
+      <c r="K790" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L790" t="inlineStr">
         <is>
           <t>USD</t>
@@ -50994,7 +51362,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K794" t="inlineStr"/>
+      <c r="K794" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L794" t="inlineStr">
         <is>
           <t>USD</t>
@@ -51693,7 +52065,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K805" t="inlineStr"/>
+      <c r="K805" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L805" t="inlineStr">
         <is>
           <t>USD</t>
@@ -52014,7 +52390,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K810" t="inlineStr"/>
+      <c r="K810" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L810" t="inlineStr">
         <is>
           <t>USD</t>
@@ -52136,7 +52516,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K812" t="inlineStr"/>
+      <c r="K812" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L812" t="inlineStr">
         <is>
           <t>USD</t>
@@ -52197,7 +52581,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K813" t="inlineStr"/>
+      <c r="K813" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L813" t="inlineStr">
         <is>
           <t>USD</t>
@@ -52965,7 +53353,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K825" t="inlineStr"/>
+      <c r="K825" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L825" t="inlineStr">
         <is>
           <t>USD</t>
@@ -53286,7 +53678,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K830" t="inlineStr"/>
+      <c r="K830" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L830" t="inlineStr">
         <is>
           <t>USD</t>
@@ -53920,7 +54316,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K840" t="inlineStr"/>
+      <c r="K840" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L840" t="inlineStr">
         <is>
           <t>USD</t>
@@ -54757,7 +55157,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K853" t="inlineStr"/>
+      <c r="K853" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L853" t="inlineStr">
         <is>
           <t>USD</t>
@@ -55078,7 +55482,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K858" t="inlineStr"/>
+      <c r="K858" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L858" t="inlineStr">
         <is>
           <t>USD</t>
@@ -56553,7 +56961,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K881" t="inlineStr"/>
+      <c r="K881" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L881" t="inlineStr">
         <is>
           <t>USD</t>
@@ -56809,7 +57221,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K885" t="inlineStr"/>
+      <c r="K885" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L885" t="inlineStr">
         <is>
           <t>USD</t>
@@ -56935,7 +57351,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K887" t="inlineStr"/>
+      <c r="K887" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L887" t="inlineStr">
         <is>
           <t>USD</t>
@@ -56996,7 +57416,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K888" t="inlineStr"/>
+      <c r="K888" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L888" t="inlineStr">
         <is>
           <t>USD</t>
@@ -57122,7 +57546,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K890" t="inlineStr"/>
+      <c r="K890" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L890" t="inlineStr">
         <is>
           <t>USD</t>
@@ -57378,7 +57806,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K894" t="inlineStr"/>
+      <c r="K894" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L894" t="inlineStr">
         <is>
           <t>USD</t>
@@ -57691,7 +58123,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K899" t="inlineStr"/>
+      <c r="K899" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L899" t="inlineStr">
         <is>
           <t>USD</t>
@@ -58264,7 +58700,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K908" t="inlineStr"/>
+      <c r="K908" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L908" t="inlineStr">
         <is>
           <t>USD</t>
@@ -59020,7 +59460,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K920" t="inlineStr"/>
+      <c r="K920" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L920" t="inlineStr">
         <is>
           <t>USD</t>
@@ -59455,7 +59899,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K927" t="inlineStr"/>
+      <c r="K927" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L927" t="inlineStr">
         <is>
           <t>USD</t>
@@ -59577,7 +60025,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K929" t="inlineStr"/>
+      <c r="K929" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L929" t="inlineStr">
         <is>
           <t>USD</t>
@@ -59699,7 +60151,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K931" t="inlineStr"/>
+      <c r="K931" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L931" t="inlineStr">
         <is>
           <t>USD</t>
@@ -59886,7 +60342,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K934" t="inlineStr"/>
+      <c r="K934" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L934" t="inlineStr">
         <is>
           <t>USD</t>
@@ -60394,7 +60854,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K942" t="inlineStr"/>
+      <c r="K942" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L942" t="inlineStr">
         <is>
           <t>USD</t>
@@ -61479,7 +61943,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K959" t="inlineStr"/>
+      <c r="K959" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L959" t="inlineStr">
         <is>
           <t>USD</t>
@@ -61666,7 +62134,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K962" t="inlineStr"/>
+      <c r="K962" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L962" t="inlineStr">
         <is>
           <t>USD</t>
@@ -61727,7 +62199,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K963" t="inlineStr"/>
+      <c r="K963" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L963" t="inlineStr">
         <is>
           <t>USD</t>
@@ -61918,7 +62394,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K966" t="inlineStr"/>
+      <c r="K966" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L966" t="inlineStr">
         <is>
           <t>USD</t>
@@ -62044,7 +62524,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K968" t="inlineStr"/>
+      <c r="K968" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L968" t="inlineStr">
         <is>
           <t>USD</t>
@@ -62877,7 +63361,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K981" t="inlineStr"/>
+      <c r="K981" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L981" t="inlineStr">
         <is>
           <t>USD</t>
@@ -63771,7 +64259,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K995" t="inlineStr"/>
+      <c r="K995" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L995" t="inlineStr">
         <is>
           <t>USD</t>
@@ -64015,7 +64507,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K999" t="inlineStr"/>
+      <c r="K999" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L999" t="inlineStr">
         <is>
           <t>USD</t>
@@ -64206,7 +64702,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K1002" t="inlineStr"/>
+      <c r="K1002" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L1002" t="inlineStr">
         <is>
           <t>USD</t>
@@ -64393,7 +64893,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K1005" t="inlineStr"/>
+      <c r="K1005" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L1005" t="inlineStr">
         <is>
           <t>USD</t>
@@ -64454,7 +64958,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K1006" t="inlineStr"/>
+      <c r="K1006" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L1006" t="inlineStr">
         <is>
           <t>USD</t>
@@ -66177,7 +66685,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K1033" t="inlineStr"/>
+      <c r="K1033" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L1033" t="inlineStr">
         <is>
           <t>USD</t>
@@ -67010,7 +67522,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K1046" t="inlineStr"/>
+      <c r="K1046" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L1046" t="inlineStr">
         <is>
           <t>USD</t>
@@ -67201,7 +67717,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K1049" t="inlineStr"/>
+      <c r="K1049" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L1049" t="inlineStr">
         <is>
           <t>USD</t>
@@ -67453,7 +67973,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K1053" t="inlineStr"/>
+      <c r="K1053" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L1053" t="inlineStr">
         <is>
           <t>USD</t>
@@ -67709,7 +68233,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K1057" t="inlineStr"/>
+      <c r="K1057" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L1057" t="inlineStr">
         <is>
           <t>USD</t>
@@ -68851,7 +69379,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K1075" t="inlineStr"/>
+      <c r="K1075" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L1075" t="inlineStr">
         <is>
           <t>USD</t>
@@ -69229,7 +69761,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K1081" t="inlineStr"/>
+      <c r="K1081" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L1081" t="inlineStr">
         <is>
           <t>USD</t>
@@ -69550,7 +70086,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K1086" t="inlineStr"/>
+      <c r="K1086" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L1086" t="inlineStr">
         <is>
           <t>USD</t>
@@ -69802,7 +70342,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K1090" t="inlineStr"/>
+      <c r="K1090" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L1090" t="inlineStr">
         <is>
           <t>USD</t>
@@ -69989,7 +70533,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K1093" t="inlineStr"/>
+      <c r="K1093" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L1093" t="inlineStr">
         <is>
           <t>USD</t>
@@ -71277,7 +71825,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K1113" t="inlineStr"/>
+      <c r="K1113" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L1113" t="inlineStr">
         <is>
           <t>USD</t>
